--- a/barbara_new/dataset_label_patter/images_results/random_forest/Random Forest importances.xlsx
+++ b/barbara_new/dataset_label_patter/images_results/random_forest/Random Forest importances.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\babac\Documents\Universita Magistrale-PoliTo\Secondo Anno\TESI\codes\ai4biological-pattern\ai4biological-pattern\barbara_new\dataset_label_patter\images_results\random_forest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{742E3E43-9C64-48CA-B897-1656E957FA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5EC9AD9-0339-4C1D-8371-E81861DEF380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3B70E69E-A164-48CE-90FA-12FA33636BC9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EA964CA5-8E85-400D-8C85-8C255BB81DBD}"/>
   </bookViews>
   <sheets>
     <sheet name="True Positive" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="494">
   <si>
     <t>feature</t>
   </si>
@@ -34,1711 +34,1477 @@
     <t>trait_rounded_at_the_base_freq</t>
   </si>
   <si>
-    <t>0.08578519014763203</t>
-  </si>
-  <si>
-    <t>trait_alternate_distally_freq</t>
-  </si>
-  <si>
-    <t>0.08305631346976156</t>
+    <t>0.09907376211625206</t>
   </si>
   <si>
     <t>trait_rounded_at_the_base_present</t>
   </si>
   <si>
-    <t>0.06497914616721161</t>
-  </si>
-  <si>
-    <t>trait_alternate_distally_present</t>
-  </si>
-  <si>
-    <t>0.06396399437008006</t>
+    <t>0.0983806651367315</t>
+  </si>
+  <si>
+    <t>trait_flowers_in_whorled_clusters_present</t>
+  </si>
+  <si>
+    <t>0.05353903357792739</t>
   </si>
   <si>
     <t>background_frac</t>
   </si>
   <si>
-    <t>0.05155489434179463</t>
-  </si>
-  <si>
-    <t>trait_with_flowers_in_whorled_clusters_present</t>
-  </si>
-  <si>
-    <t>0.04984097929968872</t>
+    <t>0.051000267378174424</t>
+  </si>
+  <si>
+    <t>trait_flowers_in_whorled_clusters_freq</t>
+  </si>
+  <si>
+    <t>0.048477606144332386</t>
+  </si>
+  <si>
+    <t>trait_erect_freq</t>
+  </si>
+  <si>
+    <t>0.04193991975835768</t>
   </si>
   <si>
     <t>hand_frac</t>
   </si>
   <si>
-    <t>0.042354685404562414</t>
+    <t>0.04155791787973613</t>
+  </si>
+  <si>
+    <t>trait_density</t>
+  </si>
+  <si>
+    <t>0.03979125075893664</t>
+  </si>
+  <si>
+    <t>trait_attenuate_at_the_base_present</t>
+  </si>
+  <si>
+    <t>0.03541995289578159</t>
+  </si>
+  <si>
+    <t>trait_attenuate_at_the_base_freq</t>
+  </si>
+  <si>
+    <t>0.03464124696476939</t>
+  </si>
+  <si>
+    <t>trait_inflorescence_raceme_present</t>
+  </si>
+  <si>
+    <t>0.030324533487485046</t>
+  </si>
+  <si>
+    <t>trait_calyx_with_alternate_long_and_small_teeth_freq</t>
+  </si>
+  <si>
+    <t>0.029749252700393473</t>
+  </si>
+  <si>
+    <t>trait_calyx_with_alternate_long_and_small_teeth_present</t>
+  </si>
+  <si>
+    <t>0.026853705277168367</t>
   </si>
   <si>
     <t>trait_diversity</t>
   </si>
   <si>
-    <t>0.03589263317375652</t>
-  </si>
-  <si>
-    <t>trait_with_flowers_in_whorled_clusters_freq</t>
-  </si>
-  <si>
-    <t>0.03485985849012034</t>
-  </si>
-  <si>
-    <t>trait_calyx_with_alternate_long_and_small_teeth_freq</t>
-  </si>
-  <si>
-    <t>0.03130218056207151</t>
-  </si>
-  <si>
-    <t>trait_erect_freq</t>
-  </si>
-  <si>
-    <t>0.030450163520264337</t>
-  </si>
-  <si>
-    <t>trait_density</t>
-  </si>
-  <si>
-    <t>0.03043274540290458</t>
-  </si>
-  <si>
-    <t>trait_calyx_with_alternate_long_and_small_teeth_present</t>
-  </si>
-  <si>
-    <t>0.023485494639897225</t>
-  </si>
-  <si>
-    <t>trait_inflorescence_raceme_present</t>
-  </si>
-  <si>
-    <t>0.023274192708460043</t>
+    <t>0.02373059249545552</t>
+  </si>
+  <si>
+    <t>trait_inflorescence_raceme_freq</t>
+  </si>
+  <si>
+    <t>0.022872791110169807</t>
   </si>
   <si>
     <t>trait_sessile_freq</t>
   </si>
   <si>
-    <t>0.022593733117099567</t>
-  </si>
-  <si>
-    <t>trait_base_attenuate_present</t>
-  </si>
-  <si>
-    <t>0.021637395167732765</t>
-  </si>
-  <si>
-    <t>trait_inflorescence_raceme_freq</t>
-  </si>
-  <si>
-    <t>0.02091359082556093</t>
-  </si>
-  <si>
-    <t>trait_becoming_alternate_distally_freq</t>
-  </si>
-  <si>
-    <t>0.019440293953927653</t>
-  </si>
-  <si>
-    <t>trait_getting_narrower_at_the_base_freq</t>
-  </si>
-  <si>
-    <t>0.019272529261205422</t>
+    <t>0.02129234773652745</t>
   </si>
   <si>
     <t>n_regions</t>
   </si>
   <si>
-    <t>0.01744873336297723</t>
-  </si>
-  <si>
-    <t>trait_base_attenuate_freq</t>
-  </si>
-  <si>
-    <t>0.01649610378815159</t>
+    <t>0.017969287334567655</t>
+  </si>
+  <si>
+    <t>trait_inflorescence_spikelike_present</t>
+  </si>
+  <si>
+    <t>0.017503399988499698</t>
+  </si>
+  <si>
+    <t>trait_narrower_at_the_base_freq</t>
+  </si>
+  <si>
+    <t>0.017066695853799774</t>
+  </si>
+  <si>
+    <t>trait_floral_tube_cylindrical_freq</t>
+  </si>
+  <si>
+    <t>0.015527094578879736</t>
   </si>
   <si>
     <t>trait_inflorescence_spikelike_freq</t>
   </si>
   <si>
-    <t>0.015154374444262377</t>
-  </si>
-  <si>
-    <t>trait_getting_narrower_at_the_base_present</t>
-  </si>
-  <si>
-    <t>0.01454243389838483</t>
+    <t>0.01542052048335934</t>
+  </si>
+  <si>
+    <t>trait_opposite,_becoming_alternate_distally_freq</t>
+  </si>
+  <si>
+    <t>0.014646988335040377</t>
   </si>
   <si>
     <t>trait_sessile_present</t>
   </si>
   <si>
-    <t>0.013969793290991217</t>
-  </si>
-  <si>
-    <t>trait_floral_tube_cylindrical_freq</t>
-  </si>
-  <si>
-    <t>0.013798916488471116</t>
+    <t>0.014111418211618414</t>
   </si>
   <si>
     <t>trait_stamens_12_freq</t>
   </si>
   <si>
-    <t>0.012967831239919524</t>
+    <t>0.013457187533440235</t>
+  </si>
+  <si>
+    <t>trait_narrower_at_the_base_present</t>
+  </si>
+  <si>
+    <t>0.012997129708182217</t>
   </si>
   <si>
     <t>trait_stamens_12_present</t>
   </si>
   <si>
-    <t>0.012934883800974357</t>
-  </si>
-  <si>
-    <t>trait_leaves_opposite_freq</t>
-  </si>
-  <si>
-    <t>0.011081952969135256</t>
-  </si>
-  <si>
-    <t>trait_becoming_alternate_distally_present</t>
-  </si>
-  <si>
-    <t>0.007962476524073047</t>
-  </si>
-  <si>
-    <t>trait_inflorescence_spikelike_present</t>
-  </si>
-  <si>
-    <t>0.007458540692102171</t>
+    <t>0.011944280470079248</t>
+  </si>
+  <si>
+    <t>trait_petals_purple_freq</t>
+  </si>
+  <si>
+    <t>0.011530029217237852</t>
+  </si>
+  <si>
+    <t>trait_petals_purple_present</t>
+  </si>
+  <si>
+    <t>0.01102724661511813</t>
+  </si>
+  <si>
+    <t>trait_opposite_freq</t>
+  </si>
+  <si>
+    <t>0.010902478225791394</t>
+  </si>
+  <si>
+    <t>trait_floral_tube_cylindrical_present</t>
+  </si>
+  <si>
+    <t>0.010549671702837294</t>
   </si>
   <si>
     <t>trait_erect_present</t>
   </si>
   <si>
-    <t>0.006703870267256829</t>
-  </si>
-  <si>
-    <t>trait_petals_rose_to_purple_freq</t>
-  </si>
-  <si>
-    <t>0.006427190986819461</t>
-  </si>
-  <si>
-    <t>trait_petals_purple_freq</t>
-  </si>
-  <si>
-    <t>0.0055503427070694</t>
+    <t>0.008709890396449663</t>
   </si>
   <si>
     <t>trait_stamens_6_present</t>
   </si>
   <si>
-    <t>0.0047241246983376235</t>
+    <t>0.007075245198307458</t>
+  </si>
+  <si>
+    <t>trait_stamens_6_freq</t>
+  </si>
+  <si>
+    <t>0.006506803822070295</t>
+  </si>
+  <si>
+    <t>trait_opposite,_becoming_alternate_distally_present</t>
+  </si>
+  <si>
+    <t>0.006099545719816739</t>
   </si>
   <si>
     <t>trait_stamens_10_14_freq</t>
   </si>
   <si>
-    <t>0.004530128756343057</t>
-  </si>
-  <si>
-    <t>trait_petals_purple_present</t>
-  </si>
-  <si>
-    <t>0.004444547173577403</t>
+    <t>0.005727686040746765</t>
+  </si>
+  <si>
+    <t>trait_inflorescence_spikelike_to_raceme_freq</t>
+  </si>
+  <si>
+    <t>0.00461356661688564</t>
+  </si>
+  <si>
+    <t>trait_stamens_10_14_present</t>
+  </si>
+  <si>
+    <t>0.004517434414286996</t>
+  </si>
+  <si>
+    <t>trait_prostrate_and_spreading_present</t>
+  </si>
+  <si>
+    <t>0.004418981407445764</t>
+  </si>
+  <si>
+    <t>trait_stamens_5_8_freq</t>
+  </si>
+  <si>
+    <t>0.00351491798030038</t>
+  </si>
+  <si>
+    <t>trait_opposite_present</t>
+  </si>
+  <si>
+    <t>0.003485475572462429</t>
+  </si>
+  <si>
+    <t>trait_stamens_5_8_present</t>
+  </si>
+  <si>
+    <t>0.0034502653937750695</t>
+  </si>
+  <si>
+    <t>trait_petals_pink_to_purple_freq</t>
+  </si>
+  <si>
+    <t>0.003161562947244913</t>
+  </si>
+  <si>
+    <t>trait_prostrate_and_spreading_freq</t>
+  </si>
+  <si>
+    <t>0.0030293537050194923</t>
+  </si>
+  <si>
+    <t>trait_linear_present</t>
+  </si>
+  <si>
+    <t>0.0028492036029415437</t>
+  </si>
+  <si>
+    <t>trait_subsessile_freq</t>
+  </si>
+  <si>
+    <t>0.0026889726172062357</t>
+  </si>
+  <si>
+    <t>trait_petals_pink_to_purple_present</t>
+  </si>
+  <si>
+    <t>0.0026166554289700607</t>
+  </si>
+  <si>
+    <t>trait_alternate_present</t>
+  </si>
+  <si>
+    <t>0.0025392866249417285</t>
   </si>
   <si>
     <t>trait_inflorescence_spikelike_to_raceme_present</t>
   </si>
   <si>
-    <t>0.003946743124099276</t>
-  </si>
-  <si>
-    <t>trait_petals_rose_to_purple_present</t>
-  </si>
-  <si>
-    <t>0.0039042716561122877</t>
-  </si>
-  <si>
-    <t>trait_floral_tube_cylindrical_present</t>
-  </si>
-  <si>
-    <t>0.0038462022736252943</t>
-  </si>
-  <si>
-    <t>trait_sessile_base_narrowly_attenuate_present</t>
-  </si>
-  <si>
-    <t>0.003477573466231553</t>
-  </si>
-  <si>
-    <t>trait_inflorescence_spikelike_to_raceme_freq</t>
-  </si>
-  <si>
-    <t>0.0033242420391074584</t>
-  </si>
-  <si>
-    <t>trait_stamens_10_14_present</t>
-  </si>
-  <si>
-    <t>0.0031318856890223358</t>
-  </si>
-  <si>
-    <t>trait_leaves_opposite_present</t>
-  </si>
-  <si>
-    <t>0.003085501825240164</t>
-  </si>
-  <si>
-    <t>trait_subsessile_freq</t>
-  </si>
-  <si>
-    <t>0.002664963709900116</t>
-  </si>
-  <si>
-    <t>trait_stamens_5_8_present</t>
-  </si>
-  <si>
-    <t>0.00262975322283337</t>
-  </si>
-  <si>
-    <t>trait_stamens_6_freq</t>
-  </si>
-  <si>
-    <t>0.0025412542186023963</t>
-  </si>
-  <si>
-    <t>trait_leaves_alternate_present</t>
-  </si>
-  <si>
-    <t>0.002511639190720451</t>
-  </si>
-  <si>
-    <t>trait_leaves_alternate_freq</t>
-  </si>
-  <si>
-    <t>0.0024687246958945575</t>
-  </si>
-  <si>
-    <t>trait_distally_alternate_present</t>
-  </si>
-  <si>
-    <t>0.0021063836635868017</t>
-  </si>
-  <si>
-    <t>trait_sessile_base_narrowly_attenuate_freq</t>
-  </si>
-  <si>
-    <t>0.0019331589134747324</t>
+    <t>0.002420080770404829</t>
+  </si>
+  <si>
+    <t>trait_alternate_freq</t>
+  </si>
+  <si>
+    <t>0.0024076993352993227</t>
+  </si>
+  <si>
+    <t>trait_petals_white_to_pink_present</t>
+  </si>
+  <si>
+    <t>0.0020692957015674713</t>
   </si>
   <si>
     <t>trait_linear_freq</t>
   </si>
   <si>
-    <t>0.0019067037197504186</t>
+    <t>0.0018314552021699857</t>
+  </si>
+  <si>
+    <t>trait_petals_white_to_pink_freq</t>
+  </si>
+  <si>
+    <t>0.0017482332907645462</t>
+  </si>
+  <si>
+    <t>trait_obtuse_to_truncate_at_the_base_present</t>
+  </si>
+  <si>
+    <t>0.0017274630234777788</t>
   </si>
   <si>
     <t>trait_subsessile_present</t>
   </si>
   <si>
-    <t>0.0018231252881523035</t>
-  </si>
-  <si>
-    <t>trait_prostrate_and_spreading_present</t>
-  </si>
-  <si>
-    <t>0.0018140689194619144</t>
-  </si>
-  <si>
-    <t>trait_distally_alternate_freq</t>
-  </si>
-  <si>
-    <t>0.0018053126951525522</t>
+    <t>0.00167085797207795</t>
+  </si>
+  <si>
+    <t>trait_floral_tube_campanulate_freq</t>
+  </si>
+  <si>
+    <t>0.0014042606454285932</t>
+  </si>
+  <si>
+    <t>trait_petiolated_present</t>
+  </si>
+  <si>
+    <t>0.0012359189054317956</t>
+  </si>
+  <si>
+    <t>trait_floral_tube_campanulate_present</t>
+  </si>
+  <si>
+    <t>0.0011541159962149736</t>
   </si>
   <si>
     <t>trait_floral_tube_obconic_present</t>
   </si>
   <si>
-    <t>0.0017560886400535864</t>
-  </si>
-  <si>
-    <t>trait_base_obtuse_to_truncate_present</t>
-  </si>
-  <si>
-    <t>0.0016491728999574649</t>
-  </si>
-  <si>
-    <t>trait_stamens_5_8_freq</t>
-  </si>
-  <si>
-    <t>0.0015074473557289444</t>
-  </si>
-  <si>
-    <t>trait_base_obtuse_to_truncate_freq</t>
-  </si>
-  <si>
-    <t>0.0012785538372942177</t>
-  </si>
-  <si>
-    <t>trait_solitary_in_leaf_axils_present</t>
-  </si>
-  <si>
-    <t>0.001211752776298778</t>
-  </si>
-  <si>
-    <t>trait_prostrate_and_spreading_freq</t>
-  </si>
-  <si>
-    <t>0.0011379991793700013</t>
-  </si>
-  <si>
-    <t>trait_petals_white_to_pink_freq</t>
-  </si>
-  <si>
-    <t>0.0008591660162670354</t>
-  </si>
-  <si>
-    <t>trait_red_dotted_freq</t>
-  </si>
-  <si>
-    <t>0.0008533140215646077</t>
+    <t>0.0010838346004270899</t>
   </si>
   <si>
     <t>trait_sprawling_or_ascending_present</t>
   </si>
   <si>
-    <t>0.0007914843767478349</t>
-  </si>
-  <si>
-    <t>trait_linear_present</t>
-  </si>
-  <si>
-    <t>0.0007693442530750229</t>
+    <t>0.0010822232100055158</t>
   </si>
   <si>
     <t>trait_sprawling_or_ascending_freq</t>
   </si>
   <si>
-    <t>0.0006519755145191142</t>
-  </si>
-  <si>
-    <t>trait_floral_tube_campanulate_freq</t>
-  </si>
-  <si>
-    <t>0.0006279122577710129</t>
-  </si>
-  <si>
-    <t>trait_red_dotted_present</t>
-  </si>
-  <si>
-    <t>0.00047640092991294903</t>
+    <t>0.001006460033218488</t>
+  </si>
+  <si>
+    <t>trait_flowers_solitary_in_leaf_axils_present</t>
+  </si>
+  <si>
+    <t>0.0009841065289800668</t>
+  </si>
+  <si>
+    <t>trait_a_discernible_gap_between_the_stem_and_the_base_of_the_blade_freq</t>
+  </si>
+  <si>
+    <t>0.0008594461572755438</t>
+  </si>
+  <si>
+    <t>trait_floral_tube_obconic_freq</t>
+  </si>
+  <si>
+    <t>0.0008404270772448961</t>
+  </si>
+  <si>
+    <t>trait_petiolated_freq</t>
+  </si>
+  <si>
+    <t>0.000684427050042713</t>
+  </si>
+  <si>
+    <t>trait_a_discernible_gap_between_the_stem_and_the_base_of_the_blade_present</t>
+  </si>
+  <si>
+    <t>0.0006568859072735216</t>
+  </si>
+  <si>
+    <t>trait_obtuse_to_truncate_at_the_base_freq</t>
+  </si>
+  <si>
+    <t>0.0006545886498084729</t>
+  </si>
+  <si>
+    <t>trait_flowers_solitary_in_leaf_axils_freq</t>
+  </si>
+  <si>
+    <t>0.00048719313832349683</t>
   </si>
   <si>
     <t>trait_prostrate_present</t>
   </si>
   <si>
-    <t>0.00037610039233759317</t>
+    <t>0.00045493314297603425</t>
+  </si>
+  <si>
+    <t>trait_creeping_to_weakly_erect_freq</t>
+  </si>
+  <si>
+    <t>0.0004034834479640512</t>
+  </si>
+  <si>
+    <t>trait_creeping_to_weakly_erect_present</t>
+  </si>
+  <si>
+    <t>0.0003943254500586689</t>
+  </si>
+  <si>
+    <t>trait_prostrate_freq</t>
+  </si>
+  <si>
+    <t>0.00037937057367579716</t>
+  </si>
+  <si>
+    <t>trait_floral_tube_obconic_without_red_dots_present</t>
+  </si>
+  <si>
+    <t>0.0003649992866737086</t>
+  </si>
+  <si>
+    <t>trait_one_or_few_flowers_in_the_axil_of_leaves_freq</t>
+  </si>
+  <si>
+    <t>0.00028739415255518377</t>
+  </si>
+  <si>
+    <t>trait_floral_tube_red_dotted_freq</t>
+  </si>
+  <si>
+    <t>0.00025957157965345376</t>
+  </si>
+  <si>
+    <t>trait_needle_like_present</t>
+  </si>
+  <si>
+    <t>0.0002316548852203518</t>
+  </si>
+  <si>
+    <t>trait_obovate_present</t>
+  </si>
+  <si>
+    <t>0.0002045400465987909</t>
+  </si>
+  <si>
+    <t>trait_erect_or_decumbent_present</t>
+  </si>
+  <si>
+    <t>0.0001859699339659508</t>
   </si>
   <si>
     <t>trait_prostrate_to_weakly_erect_present</t>
   </si>
   <si>
-    <t>0.00035297853777854494</t>
-  </si>
-  <si>
-    <t>trait_prostrate_freq</t>
-  </si>
-  <si>
-    <t>0.0003395566563719233</t>
-  </si>
-  <si>
-    <t>trait_flower_tube_narrowly_cylindrical_without_red_dots_freq</t>
-  </si>
-  <si>
-    <t>0.0003283939298035187</t>
-  </si>
-  <si>
-    <t>trait_petals_white_to_pink_present</t>
-  </si>
-  <si>
-    <t>0.0002322918144071671</t>
+    <t>0.0001809218821071781</t>
+  </si>
+  <si>
+    <t>trait_needle_like_freq</t>
+  </si>
+  <si>
+    <t>0.0001696322082293403</t>
+  </si>
+  <si>
+    <t>trait_erect_or_decumbent_freq</t>
+  </si>
+  <si>
+    <t>0.0001513741446757258</t>
+  </si>
+  <si>
+    <t>trait_obovate_freq</t>
+  </si>
+  <si>
+    <t>0.00014498227816442649</t>
+  </si>
+  <si>
+    <t>trait_petals_pink_present</t>
+  </si>
+  <si>
+    <t>0.0001354396519108598</t>
+  </si>
+  <si>
+    <t>trait_floral_tube_narrowly_cylindrical_without_red_dots_present</t>
+  </si>
+  <si>
+    <t>0.00011212281942081501</t>
+  </si>
+  <si>
+    <t>trait_one_or_few_flowers_in_the_axil_of_leaves_present</t>
+  </si>
+  <si>
+    <t>0.0001089941002587847</t>
+  </si>
+  <si>
+    <t>trait_stamens_4_6_present</t>
+  </si>
+  <si>
+    <t>0.00010639959169937234</t>
+  </si>
+  <si>
+    <t>trait_floral_tube_red_dotted_present</t>
+  </si>
+  <si>
+    <t>0.00010255760787587523</t>
   </si>
   <si>
     <t>trait_calyx_with_teeth_of_the_same_length_freq</t>
   </si>
   <si>
-    <t>0.00022932015058517061</t>
-  </si>
-  <si>
-    <t>trait_one_or_few_flowers_in_the_axil_of_leaves_present</t>
-  </si>
-  <si>
-    <t>0.00022079501843999663</t>
+    <t>trait_stamens_2_3_present</t>
+  </si>
+  <si>
+    <t>trait_flowers_solitary_present</t>
+  </si>
+  <si>
+    <t>trait_petals_minute_freq</t>
+  </si>
+  <si>
+    <t>trait_stamens_2_3_freq</t>
+  </si>
+  <si>
+    <t>trait_floral_tube_obconic_without_red_dots_freq</t>
   </si>
   <si>
     <t>trait_calyx_with_teeth_of_the_same_length_present</t>
   </si>
   <si>
-    <t>0.00020555896539708435</t>
-  </si>
-  <si>
     <t>trait_usually_with_a_darker_midrib_freq</t>
   </si>
   <si>
-    <t>0.0001979922933200285</t>
+    <t>trait_petals_minute_present</t>
+  </si>
+  <si>
+    <t>trait_creeping_present</t>
+  </si>
+  <si>
+    <t>trait_usually_with_a_darker_midrib_present</t>
   </si>
   <si>
     <t>trait_petals_pale_purple_or_whitish_present</t>
   </si>
   <si>
-    <t>0.00016858955630039415</t>
-  </si>
-  <si>
-    <t>trait_needle_like_leaves_freq</t>
-  </si>
-  <si>
-    <t>0.00016403444170722393</t>
+    <t>trait_petals_pink_freq</t>
+  </si>
+  <si>
+    <t>trait_petals_lavender_present</t>
+  </si>
+  <si>
+    <t>trait_petals_reddish_freq</t>
+  </si>
+  <si>
+    <t>trait_stamens_4_6_freq</t>
+  </si>
+  <si>
+    <t>trait_prostrate_to_weakly_erect_freq</t>
+  </si>
+  <si>
+    <t>trait_flowers_solitary_freq</t>
+  </si>
+  <si>
+    <t>trait_petals_white_present</t>
+  </si>
+  <si>
+    <t>trait_stamens_10_12_freq</t>
+  </si>
+  <si>
+    <t>trait_creeping_freq</t>
+  </si>
+  <si>
+    <t>trait_stamens_10_12_present</t>
+  </si>
+  <si>
+    <t>trait_floral_tube_narrowly_cylindrical_without_red_dots_freq</t>
+  </si>
+  <si>
+    <t>trait_sessile_or_subsessile_freq</t>
+  </si>
+  <si>
+    <t>trait_petals_white_freq</t>
+  </si>
+  <si>
+    <t>trait_sessile_or_subsessile_present</t>
+  </si>
+  <si>
+    <t>trait_petals_purple_with_a_darker_midrib_present</t>
+  </si>
+  <si>
+    <t>trait_petals_reddish_present</t>
+  </si>
+  <si>
+    <t>trait_petals_purple_with_a_darker_midrib_freq</t>
+  </si>
+  <si>
+    <t>trait_broader_at_the_base_present</t>
+  </si>
+  <si>
+    <t>trait_stamens_6_8_freq</t>
+  </si>
+  <si>
+    <t>trait_petals_lavender_freq</t>
+  </si>
+  <si>
+    <t>trait_petals_4_freq</t>
+  </si>
+  <si>
+    <t>trait_petals_4_present</t>
   </si>
   <si>
     <t>trait_petals_pale_purple_or_whitish_freq</t>
   </si>
   <si>
-    <t>0.0001625326968779009</t>
-  </si>
-  <si>
-    <t>trait_leaves_opposite_but_sometimes_alternate_freq</t>
-  </si>
-  <si>
-    <t>0.00015733018473803386</t>
-  </si>
-  <si>
-    <t>trait_one_or_few_flowers_in_the_axil_of_leaves_freq</t>
-  </si>
-  <si>
-    <t>0.00015249877539491314</t>
-  </si>
-  <si>
-    <t>trait_flower_tube_narrowly_cylindrical_without_red_dots_present</t>
-  </si>
-  <si>
-    <t>0.0001455271082504204</t>
-  </si>
-  <si>
-    <t>trait_sometimes_creeping_freq</t>
-  </si>
-  <si>
-    <t>0.00014527483717715603</t>
-  </si>
-  <si>
-    <t>trait_needle_like_leaves_present</t>
-  </si>
-  <si>
-    <t>0.0001376380838644837</t>
-  </si>
-  <si>
-    <t>trait_prostrate_to_weakly_erect_freq</t>
-  </si>
-  <si>
-    <t>0.00013529951426696782</t>
-  </si>
-  <si>
-    <t>trait_floral_tube_obconic_freq</t>
-  </si>
-  <si>
-    <t>0.0001289140208085908</t>
-  </si>
-  <si>
-    <t>trait_stamens_4_6_present</t>
-  </si>
-  <si>
-    <t>0.00011999376765216178</t>
-  </si>
-  <si>
-    <t>trait_stamens_2_3_present</t>
-  </si>
-  <si>
-    <t>0.00011206031292944936</t>
-  </si>
-  <si>
-    <t>trait_leaves_opposite_but_sometimes_alternate_present</t>
-  </si>
-  <si>
-    <t>0.00010474575879567666</t>
-  </si>
-  <si>
-    <t>trait_obovate_freq</t>
-  </si>
-  <si>
-    <t>0.00010374797796651693</t>
-  </si>
-  <si>
-    <t>trait_solitary_in_leaf_axils_freq</t>
-  </si>
-  <si>
-    <t>0.00010304724123320604</t>
-  </si>
-  <si>
-    <t>trait_obovate_present</t>
-  </si>
-  <si>
-    <t>0.0001015745345228523</t>
-  </si>
-  <si>
-    <t>trait_base_rounded_present</t>
-  </si>
-  <si>
-    <t>trait_rounded_base_present</t>
-  </si>
-  <si>
-    <t>trait_rounded_base_freq</t>
-  </si>
-  <si>
-    <t>trait_petals_pinkish_to_white_present</t>
-  </si>
-  <si>
-    <t>trait_a_discernible_gap_between_the_stem_and_the_base_of_the_blade_freq</t>
-  </si>
-  <si>
-    <t>trait_sometimes_creeping_present</t>
-  </si>
-  <si>
-    <t>trait_creeping_freq</t>
-  </si>
-  <si>
-    <t>trait_creeping_present</t>
-  </si>
-  <si>
-    <t>trait_petals_pinkish_to_white_freq</t>
-  </si>
-  <si>
-    <t>trait_a_discernible_gap_between_the_stem_and_the_base_of_the_blade_present</t>
-  </si>
-  <si>
-    <t>trait_purple_freq</t>
-  </si>
-  <si>
-    <t>trait_petals_pinkish_freq</t>
-  </si>
-  <si>
-    <t>trait_creeping_to_weakly_erect_present</t>
-  </si>
-  <si>
-    <t>trait_stamens_2_3_freq</t>
-  </si>
-  <si>
-    <t>trait_creeping_to_weakly_erect_freq</t>
-  </si>
-  <si>
-    <t>trait_petiolated_present</t>
-  </si>
-  <si>
-    <t>trait_often_with_a_darker_midrib_freq</t>
-  </si>
-  <si>
-    <t>trait_purple_present</t>
-  </si>
-  <si>
-    <t>trait_flowers_solitary_freq</t>
-  </si>
-  <si>
-    <t>trait_base_rounded_freq</t>
-  </si>
-  <si>
-    <t>trait_sometimes_alternate_distally_present</t>
-  </si>
-  <si>
-    <t>trait_stamens_4_6_freq</t>
-  </si>
-  <si>
-    <t>trait_petals_minute_freq</t>
-  </si>
-  <si>
-    <t>trait_floral_tube_campanulate_present</t>
-  </si>
-  <si>
-    <t>trait_petals_minute_present</t>
-  </si>
-  <si>
-    <t>trait_flowers_solitary_present</t>
-  </si>
-  <si>
-    <t>trait_petiolated_freq</t>
-  </si>
-  <si>
-    <t>trait_petals_pinkish_present</t>
-  </si>
-  <si>
-    <t>trait_erect_or_decumbent_present</t>
-  </si>
-  <si>
-    <t>trait_sessile_or_subsessile_present</t>
-  </si>
-  <si>
-    <t>trait_petals_reddish_present</t>
-  </si>
-  <si>
-    <t>trait_petals_pink_to_purple_freq</t>
-  </si>
-  <si>
-    <t>trait_petals_pink_present</t>
-  </si>
-  <si>
-    <t>trait_minute_present</t>
-  </si>
-  <si>
-    <t>trait_often_with_a_darker_midrib_present</t>
-  </si>
-  <si>
-    <t>trait_sessile_or_subsessile_freq</t>
-  </si>
-  <si>
-    <t>trait_sometimes_alternate_distally_freq</t>
-  </si>
-  <si>
-    <t>trait_leaves_mostly_alternate_freq</t>
-  </si>
-  <si>
-    <t>trait_petals_white_freq</t>
-  </si>
-  <si>
-    <t>trait_petals_lavender_present</t>
-  </si>
-  <si>
-    <t>trait_petals_pink_freq</t>
-  </si>
-  <si>
-    <t>trait_petals_pink_to_purple_present</t>
-  </si>
-  <si>
-    <t>trait_floral_tube_obconic_without_red_dots_present</t>
-  </si>
-  <si>
-    <t>trait_minute_freq</t>
-  </si>
-  <si>
-    <t>trait_petals_white_present</t>
-  </si>
-  <si>
-    <t>trait_petals_reddish_freq</t>
-  </si>
-  <si>
-    <t>trait_erect_or_decumbent_freq</t>
-  </si>
-  <si>
-    <t>trait_leaves_mostly_alternate_present</t>
-  </si>
-  <si>
-    <t>trait_base_narrowly_attenuate_present</t>
-  </si>
-  <si>
-    <t>trait_usually_with_a_darker_midrib_present</t>
-  </si>
-  <si>
-    <t>trait_petals_lavender_freq</t>
-  </si>
-  <si>
-    <t>trait_leaves_with_petiole_freq</t>
-  </si>
-  <si>
-    <t>trait_petals_pale_purple_to_purple_sometimes_with_red_midribs_present</t>
-  </si>
-  <si>
     <t>trait_stamens_8_freq</t>
   </si>
   <si>
-    <t>trait_floral_tube_narrowly_obconic_without_red_dots_freq</t>
-  </si>
-  <si>
-    <t>trait_stamens_10_12_present</t>
-  </si>
-  <si>
-    <t>trait_leaves_sessile_freq</t>
+    <t>trait_petals_pink_to_purple_with_a_darker_midrib_freq</t>
+  </si>
+  <si>
+    <t>trait_broader_at_the_base_freq</t>
+  </si>
+  <si>
+    <t>trait_stamens_6_8_present</t>
+  </si>
+  <si>
+    <t>trait_petals_pink_to_purple_with_a_darker_midrib_present</t>
+  </si>
+  <si>
+    <t>trait_petals_lilac_to_pink_freq</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>trait_petals_lilac_to_pink_present</t>
   </si>
   <si>
     <t>trait_stamens_8_present</t>
   </si>
   <si>
-    <t>trait_leaves_with_petiole_present</t>
-  </si>
-  <si>
-    <t>trait_broader_at_the_base_freq</t>
-  </si>
-  <si>
-    <t>trait_petals_pink_to_purple_with_a_darker_midrib_freq</t>
-  </si>
-  <si>
-    <t>trait_petals_pale_purple_to_purple_present</t>
-  </si>
-  <si>
-    <t>trait_petals_pink_to_purple_with_a_darker_midrib_present</t>
-  </si>
-  <si>
-    <t>trait_leaves_sessile_present</t>
-  </si>
-  <si>
-    <t>trait_4_minute_petals_freq</t>
-  </si>
-  <si>
-    <t>trait_base_narrowly_attenuate_freq</t>
-  </si>
-  <si>
-    <t>trait_stamens_6_8_freq</t>
-  </si>
-  <si>
-    <t>trait_pink_freq</t>
-  </si>
-  <si>
-    <t>trait_pink_present</t>
-  </si>
-  <si>
-    <t>trait_4_minute_petals_present</t>
-  </si>
-  <si>
-    <t>trait_petals_lilac_to_pink_freq</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>trait_petals_4_freq</t>
-  </si>
-  <si>
-    <t>trait_purple_with_a_darker_midrib_freq</t>
-  </si>
-  <si>
-    <t>trait_petals_4_present</t>
-  </si>
-  <si>
-    <t>trait_purple_with_a_darker_midrib_present</t>
-  </si>
-  <si>
-    <t>trait_stamens_6_8_present</t>
-  </si>
-  <si>
-    <t>trait_floral_tube_obconic_without_red_dots_freq</t>
-  </si>
-  <si>
-    <t>trait_petals_pale_purple_to_purple_sometimes_with_red_midribs_freq</t>
-  </si>
-  <si>
-    <t>trait_petals_lilac_to_pink_present</t>
-  </si>
-  <si>
-    <t>trait_broader_at_the_base_present</t>
-  </si>
-  <si>
-    <t>trait_stamens_10_12_freq</t>
-  </si>
-  <si>
-    <t>trait_floral_tube_narrowly_obconic_without_red_dots_present</t>
-  </si>
-  <si>
-    <t>trait_petals_pale_purple_to_purple_freq</t>
-  </si>
-  <si>
-    <t>0.0001019781243528107</t>
-  </si>
-  <si>
-    <t>0.00010450608493851437</t>
-  </si>
-  <si>
-    <t>0.00010683502301070345</t>
-  </si>
-  <si>
-    <t>0.00011089679903175235</t>
-  </si>
-  <si>
-    <t>0.00011224201500879446</t>
-  </si>
-  <si>
-    <t>0.00011539756225624415</t>
-  </si>
-  <si>
-    <t>0.00012041207279394878</t>
-  </si>
-  <si>
-    <t>0.00012175584726998169</t>
-  </si>
-  <si>
-    <t>0.00012541363342465938</t>
-  </si>
-  <si>
-    <t>0.00014015872255009534</t>
-  </si>
-  <si>
-    <t>0.00015640793662612446</t>
-  </si>
-  <si>
-    <t>0.00016126747583018546</t>
-  </si>
-  <si>
-    <t>0.00017260728586014772</t>
-  </si>
-  <si>
-    <t>0.0001871599284540173</t>
-  </si>
-  <si>
-    <t>0.00019117254272428408</t>
-  </si>
-  <si>
-    <t>0.0002095100470769808</t>
-  </si>
-  <si>
-    <t>0.00021006764396484207</t>
-  </si>
-  <si>
-    <t>0.00021529287474647275</t>
-  </si>
-  <si>
-    <t>0.00021763436598433816</t>
-  </si>
-  <si>
-    <t>0.00021782693003259034</t>
-  </si>
-  <si>
-    <t>0.0002183609823759428</t>
-  </si>
-  <si>
-    <t>0.00021978087871651764</t>
-  </si>
-  <si>
-    <t>0.00023153497857002212</t>
-  </si>
-  <si>
-    <t>0.00027288014774319455</t>
-  </si>
-  <si>
-    <t>0.0002857660467565487</t>
-  </si>
-  <si>
-    <t>0.00030882606758871376</t>
-  </si>
-  <si>
-    <t>0.00032262663166363737</t>
-  </si>
-  <si>
-    <t>0.00032431343485687627</t>
-  </si>
-  <si>
-    <t>0.0004270714142129767</t>
-  </si>
-  <si>
-    <t>0.00044170081849168773</t>
-  </si>
-  <si>
-    <t>0.000516937113079606</t>
-  </si>
-  <si>
-    <t>0.0005996564688301516</t>
-  </si>
-  <si>
-    <t>0.0008885987489217977</t>
-  </si>
-  <si>
-    <t>0.0011663921129938522</t>
-  </si>
-  <si>
-    <t>0.0011800664588801381</t>
-  </si>
-  <si>
-    <t>0.001245307352234325</t>
-  </si>
-  <si>
-    <t>0.001453709100595987</t>
-  </si>
-  <si>
-    <t>0.0016172248886896156</t>
-  </si>
-  <si>
-    <t>0.0016347212439402066</t>
-  </si>
-  <si>
-    <t>0.0016504301248891603</t>
-  </si>
-  <si>
-    <t>0.0016950498037490908</t>
-  </si>
-  <si>
-    <t>0.0017603814593979107</t>
-  </si>
-  <si>
-    <t>0.0017731815217892466</t>
-  </si>
-  <si>
-    <t>0.0019123237805705616</t>
-  </si>
-  <si>
-    <t>0.002035528457333366</t>
-  </si>
-  <si>
-    <t>0.002111573783971071</t>
-  </si>
-  <si>
-    <t>0.0022189184001456825</t>
-  </si>
-  <si>
-    <t>0.002341880921169542</t>
-  </si>
-  <si>
-    <t>0.002765383165917977</t>
-  </si>
-  <si>
-    <t>0.0027884804488661308</t>
-  </si>
-  <si>
-    <t>0.003015463447463884</t>
-  </si>
-  <si>
-    <t>0.0033225674322096004</t>
-  </si>
-  <si>
-    <t>0.003436549529262336</t>
-  </si>
-  <si>
-    <t>0.0036896715777676777</t>
-  </si>
-  <si>
-    <t>0.003854412276891599</t>
-  </si>
-  <si>
-    <t>0.0038564133101174373</t>
-  </si>
-  <si>
-    <t>0.003943419910390073</t>
-  </si>
-  <si>
-    <t>0.004299975578409053</t>
-  </si>
-  <si>
-    <t>0.004496086718494475</t>
-  </si>
-  <si>
-    <t>0.004624103721423938</t>
-  </si>
-  <si>
-    <t>0.004719557289981375</t>
-  </si>
-  <si>
-    <t>0.005037051163102682</t>
-  </si>
-  <si>
-    <t>0.005373639570071277</t>
-  </si>
-  <si>
-    <t>0.005382208075409191</t>
-  </si>
-  <si>
-    <t>0.0055330833522413345</t>
-  </si>
-  <si>
-    <t>0.005741669765396517</t>
-  </si>
-  <si>
-    <t>0.005747599016234797</t>
-  </si>
-  <si>
-    <t>0.005756769304038137</t>
-  </si>
-  <si>
-    <t>0.0059783241923215364</t>
-  </si>
-  <si>
-    <t>0.00625560602031402</t>
-  </si>
-  <si>
-    <t>0.006391520023813196</t>
-  </si>
-  <si>
-    <t>0.006985057560183595</t>
-  </si>
-  <si>
-    <t>0.007767817941853382</t>
-  </si>
-  <si>
-    <t>0.008081347070076914</t>
-  </si>
-  <si>
-    <t>0.01249896603058373</t>
-  </si>
-  <si>
-    <t>0.013105465258937849</t>
-  </si>
-  <si>
-    <t>0.013347531307696262</t>
-  </si>
-  <si>
-    <t>0.013402998768394112</t>
-  </si>
-  <si>
-    <t>0.01369283989853369</t>
-  </si>
-  <si>
-    <t>0.014961400177459755</t>
-  </si>
-  <si>
-    <t>0.015123074767583164</t>
-  </si>
-  <si>
-    <t>0.016250188235737466</t>
-  </si>
-  <si>
-    <t>0.017830723180366437</t>
-  </si>
-  <si>
-    <t>0.020215804299144144</t>
-  </si>
-  <si>
-    <t>0.020421842576227152</t>
-  </si>
-  <si>
-    <t>0.020544406685639376</t>
-  </si>
-  <si>
-    <t>0.024412066123798478</t>
-  </si>
-  <si>
-    <t>0.0247340572247293</t>
-  </si>
-  <si>
-    <t>0.02483876191204771</t>
-  </si>
-  <si>
-    <t>0.025946793203748462</t>
-  </si>
-  <si>
-    <t>0.026573188588727564</t>
-  </si>
-  <si>
-    <t>0.026803835005302912</t>
-  </si>
-  <si>
-    <t>0.02841933542870508</t>
-  </si>
-  <si>
-    <t>0.028565546946349038</t>
-  </si>
-  <si>
-    <t>0.0380969914158108</t>
-  </si>
-  <si>
-    <t>0.06234115600735453</t>
-  </si>
-  <si>
-    <t>0.07792552333075282</t>
-  </si>
-  <si>
-    <t>0.07846090077536703</t>
-  </si>
-  <si>
-    <t>0.08561070825113383</t>
-  </si>
-  <si>
-    <t>0.09096879685475948</t>
-  </si>
-  <si>
-    <t>0.00011555926181176026</t>
-  </si>
-  <si>
-    <t>0.00011608435068879413</t>
-  </si>
-  <si>
-    <t>0.00011813529546693592</t>
-  </si>
-  <si>
-    <t>0.00011855668143983073</t>
-  </si>
-  <si>
-    <t>0.0001210643303877952</t>
-  </si>
-  <si>
-    <t>0.0001312118829034483</t>
-  </si>
-  <si>
-    <t>0.0001356047822546717</t>
-  </si>
-  <si>
-    <t>0.0001365005935710295</t>
-  </si>
-  <si>
-    <t>0.00013907034690923138</t>
-  </si>
-  <si>
-    <t>0.00014038948946380387</t>
-  </si>
-  <si>
-    <t>0.0001466529099007571</t>
-  </si>
-  <si>
-    <t>0.00015477202149087298</t>
-  </si>
-  <si>
-    <t>0.00015881653293302434</t>
-  </si>
-  <si>
-    <t>0.00016430606299916976</t>
-  </si>
-  <si>
-    <t>0.00017066302071639777</t>
-  </si>
-  <si>
-    <t>0.0001738012372209534</t>
-  </si>
-  <si>
-    <t>0.00017776249364687127</t>
-  </si>
-  <si>
-    <t>0.00018726076162458357</t>
-  </si>
-  <si>
-    <t>0.00019067898660434486</t>
-  </si>
-  <si>
-    <t>0.00019522517709891766</t>
-  </si>
-  <si>
-    <t>0.00019692181134571443</t>
-  </si>
-  <si>
-    <t>0.0002024632017233416</t>
-  </si>
-  <si>
-    <t>0.00021482759882363777</t>
-  </si>
-  <si>
-    <t>0.00021547208573587047</t>
-  </si>
-  <si>
-    <t>0.00021796900075045464</t>
-  </si>
-  <si>
-    <t>0.0002208486672928014</t>
-  </si>
-  <si>
-    <t>0.0002229611599053679</t>
-  </si>
-  <si>
-    <t>0.0002241226748513566</t>
-  </si>
-  <si>
-    <t>0.00023164934319185653</t>
-  </si>
-  <si>
-    <t>0.00025087331389948814</t>
-  </si>
-  <si>
-    <t>0.00025850361761272056</t>
-  </si>
-  <si>
-    <t>0.000273655688804984</t>
-  </si>
-  <si>
-    <t>0.0002836715777509617</t>
-  </si>
-  <si>
-    <t>0.0002842847452384053</t>
-  </si>
-  <si>
-    <t>0.00028999675166143713</t>
-  </si>
-  <si>
-    <t>0.00029806769613322344</t>
-  </si>
-  <si>
-    <t>0.00031942698015125675</t>
-  </si>
-  <si>
-    <t>0.0003244218959197149</t>
-  </si>
-  <si>
-    <t>0.00033272663398221486</t>
-  </si>
-  <si>
-    <t>0.0003355847192744878</t>
-  </si>
-  <si>
-    <t>0.0003441899885229661</t>
-  </si>
-  <si>
-    <t>0.0003727267354779524</t>
-  </si>
-  <si>
-    <t>0.00037443397580724645</t>
-  </si>
-  <si>
-    <t>0.0003787901448207093</t>
-  </si>
-  <si>
-    <t>0.0003905369954227109</t>
-  </si>
-  <si>
-    <t>0.00039785730977029524</t>
-  </si>
-  <si>
-    <t>0.0004047277517042981</t>
-  </si>
-  <si>
-    <t>0.000452236247913157</t>
-  </si>
-  <si>
-    <t>0.0004557873277617536</t>
-  </si>
-  <si>
-    <t>0.0004587781190904669</t>
-  </si>
-  <si>
-    <t>0.00046253488602437476</t>
-  </si>
-  <si>
-    <t>0.00046765229106967085</t>
-  </si>
-  <si>
-    <t>0.00048113287139844684</t>
-  </si>
-  <si>
-    <t>0.0004909225952373534</t>
-  </si>
-  <si>
-    <t>0.0004934365865366392</t>
-  </si>
-  <si>
-    <t>0.0004984965192969385</t>
-  </si>
-  <si>
-    <t>0.0005093828596737495</t>
-  </si>
-  <si>
-    <t>0.000515375078690324</t>
-  </si>
-  <si>
-    <t>0.00058517924783704</t>
-  </si>
-  <si>
-    <t>0.0006607044299994784</t>
-  </si>
-  <si>
-    <t>0.0006886791291932112</t>
-  </si>
-  <si>
-    <t>0.0007241273336683725</t>
-  </si>
-  <si>
-    <t>0.0008348186312735906</t>
-  </si>
-  <si>
-    <t>0.0008632376465839505</t>
-  </si>
-  <si>
-    <t>0.000870110005994751</t>
-  </si>
-  <si>
-    <t>0.0009345198347864759</t>
-  </si>
-  <si>
-    <t>0.0009854607043007892</t>
-  </si>
-  <si>
-    <t>0.0010714763976534993</t>
-  </si>
-  <si>
-    <t>0.001137457968899908</t>
-  </si>
-  <si>
-    <t>0.00118016630554839</t>
-  </si>
-  <si>
-    <t>0.0012180972396720444</t>
-  </si>
-  <si>
-    <t>0.001227033797999835</t>
-  </si>
-  <si>
-    <t>0.0012798602595086744</t>
-  </si>
-  <si>
-    <t>0.0013110314033969441</t>
-  </si>
-  <si>
-    <t>0.0016043174371400063</t>
-  </si>
-  <si>
-    <t>0.0017031549513860276</t>
-  </si>
-  <si>
-    <t>0.0017073878933139555</t>
-  </si>
-  <si>
-    <t>0.0017166329264566573</t>
-  </si>
-  <si>
-    <t>0.0018362456812031172</t>
-  </si>
-  <si>
-    <t>0.002158029342766269</t>
-  </si>
-  <si>
-    <t>0.002385761335886245</t>
-  </si>
-  <si>
-    <t>0.0027968949895582607</t>
-  </si>
-  <si>
-    <t>0.002936174056417637</t>
-  </si>
-  <si>
-    <t>0.002942167440863095</t>
-  </si>
-  <si>
-    <t>0.0029576214691371984</t>
-  </si>
-  <si>
-    <t>0.0029593792001548795</t>
-  </si>
-  <si>
-    <t>0.003006698382990899</t>
-  </si>
-  <si>
-    <t>0.003066426639508842</t>
-  </si>
-  <si>
-    <t>0.003069420341207151</t>
-  </si>
-  <si>
-    <t>0.003100586037341916</t>
-  </si>
-  <si>
-    <t>0.003116846742537574</t>
-  </si>
-  <si>
-    <t>0.0031284400999681663</t>
-  </si>
-  <si>
-    <t>0.003613441139496515</t>
-  </si>
-  <si>
-    <t>0.003756452276767352</t>
-  </si>
-  <si>
-    <t>0.0037682024238242084</t>
-  </si>
-  <si>
-    <t>0.0038155282964201496</t>
-  </si>
-  <si>
-    <t>0.004478907449756395</t>
-  </si>
-  <si>
-    <t>0.004774263584505266</t>
-  </si>
-  <si>
-    <t>0.005940386455538865</t>
-  </si>
-  <si>
-    <t>0.0061134233757221225</t>
-  </si>
-  <si>
-    <t>0.006510483146479373</t>
-  </si>
-  <si>
-    <t>0.007387231133714494</t>
-  </si>
-  <si>
-    <t>0.007524676656218156</t>
-  </si>
-  <si>
-    <t>0.012996595217187682</t>
-  </si>
-  <si>
-    <t>0.01885552954182588</t>
-  </si>
-  <si>
-    <t>0.020403608227001987</t>
-  </si>
-  <si>
-    <t>0.022361636913271376</t>
-  </si>
-  <si>
-    <t>0.024376139750708247</t>
-  </si>
-  <si>
-    <t>0.024772595181609916</t>
-  </si>
-  <si>
-    <t>0.030747652233513657</t>
-  </si>
-  <si>
-    <t>0.03186410950078535</t>
-  </si>
-  <si>
-    <t>0.03220695358183152</t>
-  </si>
-  <si>
-    <t>0.04313613768765804</t>
-  </si>
-  <si>
-    <t>0.044998527367711975</t>
-  </si>
-  <si>
-    <t>0.05145845314122312</t>
-  </si>
-  <si>
-    <t>0.05878445409673698</t>
-  </si>
-  <si>
-    <t>0.07898348262762939</t>
-  </si>
-  <si>
-    <t>0.08277027764621953</t>
-  </si>
-  <si>
-    <t>0.13083711232610815</t>
-  </si>
-  <si>
-    <t>0.1533090412678249</t>
-  </si>
-  <si>
-    <t>0.00010064337449260711</t>
-  </si>
-  <si>
-    <t>0.00012240499572064537</t>
-  </si>
-  <si>
-    <t>0.00012584660924975157</t>
-  </si>
-  <si>
-    <t>0.00012860312940819602</t>
-  </si>
-  <si>
-    <t>0.00013233305223048445</t>
-  </si>
-  <si>
-    <t>0.0001470606908710826</t>
-  </si>
-  <si>
-    <t>0.00018020367357702012</t>
-  </si>
-  <si>
-    <t>0.00018539569663516238</t>
-  </si>
-  <si>
-    <t>0.00019034611410420125</t>
-  </si>
-  <si>
-    <t>0.00019303371877734226</t>
-  </si>
-  <si>
-    <t>0.00020519079745713066</t>
-  </si>
-  <si>
-    <t>0.0002220923709863933</t>
-  </si>
-  <si>
-    <t>0.00022849308003520041</t>
-  </si>
-  <si>
-    <t>0.00024188559925261008</t>
-  </si>
-  <si>
-    <t>0.0002632457243247881</t>
-  </si>
-  <si>
-    <t>0.0003015850400191244</t>
-  </si>
-  <si>
-    <t>0.00030691495410186726</t>
-  </si>
-  <si>
-    <t>0.000331756202041305</t>
-  </si>
-  <si>
-    <t>0.0003448563980847175</t>
-  </si>
-  <si>
-    <t>0.0003730897172347339</t>
-  </si>
-  <si>
-    <t>0.00039369967990538385</t>
-  </si>
-  <si>
-    <t>0.00044512704526389877</t>
-  </si>
-  <si>
-    <t>0.000501393794840322</t>
-  </si>
-  <si>
-    <t>0.0005591902509762761</t>
-  </si>
-  <si>
-    <t>0.0005906129834546157</t>
-  </si>
-  <si>
-    <t>0.0006465948315971094</t>
-  </si>
-  <si>
-    <t>0.0009011515729332494</t>
-  </si>
-  <si>
-    <t>0.0009589978999645754</t>
-  </si>
-  <si>
-    <t>0.0011279290336242147</t>
-  </si>
-  <si>
-    <t>0.001202096102685064</t>
-  </si>
-  <si>
-    <t>0.001335452097383859</t>
-  </si>
-  <si>
-    <t>0.0014617663189778979</t>
-  </si>
-  <si>
-    <t>0.0016083492861616608</t>
-  </si>
-  <si>
-    <t>0.0016481170075816382</t>
-  </si>
-  <si>
-    <t>0.0017000202558877628</t>
-  </si>
-  <si>
-    <t>0.0020135035860533485</t>
-  </si>
-  <si>
-    <t>0.002187167976990801</t>
-  </si>
-  <si>
-    <t>0.0021897241208508663</t>
-  </si>
-  <si>
-    <t>0.0024719673315418433</t>
-  </si>
-  <si>
-    <t>0.0026968723893758565</t>
-  </si>
-  <si>
-    <t>0.003067110264945474</t>
-  </si>
-  <si>
-    <t>0.0035118357472332744</t>
-  </si>
-  <si>
-    <t>0.003977729527530644</t>
-  </si>
-  <si>
-    <t>0.004354390029230697</t>
-  </si>
-  <si>
-    <t>0.004577629040300565</t>
-  </si>
-  <si>
-    <t>0.004847135873838587</t>
-  </si>
-  <si>
-    <t>0.004954485419177921</t>
-  </si>
-  <si>
-    <t>0.00520827463174069</t>
-  </si>
-  <si>
-    <t>0.005612404312906703</t>
-  </si>
-  <si>
-    <t>0.0070468033501820794</t>
-  </si>
-  <si>
-    <t>0.0071504414591806575</t>
-  </si>
-  <si>
-    <t>0.007183078733853217</t>
-  </si>
-  <si>
-    <t>0.008090638345885392</t>
-  </si>
-  <si>
-    <t>0.00840843565305864</t>
-  </si>
-  <si>
-    <t>0.009099951057800431</t>
-  </si>
-  <si>
-    <t>0.009799695686545195</t>
-  </si>
-  <si>
-    <t>0.01046489500904768</t>
-  </si>
-  <si>
-    <t>0.011105750181082506</t>
-  </si>
-  <si>
-    <t>0.011404606202569804</t>
-  </si>
-  <si>
-    <t>0.013670425599629877</t>
-  </si>
-  <si>
-    <t>0.015554819598866579</t>
-  </si>
-  <si>
-    <t>0.01561264478515944</t>
-  </si>
-  <si>
-    <t>0.015895240434506654</t>
-  </si>
-  <si>
-    <t>0.01643834352868328</t>
-  </si>
-  <si>
-    <t>0.016447091774272997</t>
-  </si>
-  <si>
-    <t>0.016953922645602727</t>
-  </si>
-  <si>
-    <t>0.02084617427536726</t>
-  </si>
-  <si>
-    <t>0.024540753886987055</t>
-  </si>
-  <si>
-    <t>0.028194495165031152</t>
-  </si>
-  <si>
-    <t>0.028269165377914563</t>
-  </si>
-  <si>
-    <t>0.03035485378893271</t>
-  </si>
-  <si>
-    <t>0.03444398592936092</t>
-  </si>
-  <si>
-    <t>0.037341335791892694</t>
-  </si>
-  <si>
-    <t>0.043435581867912604</t>
-  </si>
-  <si>
-    <t>0.04549043502395181</t>
-  </si>
-  <si>
-    <t>0.04672767947854429</t>
-  </si>
-  <si>
-    <t>0.04979216325150162</t>
-  </si>
-  <si>
-    <t>0.050943028820428</t>
-  </si>
-  <si>
-    <t>0.06213805238943278</t>
-  </si>
-  <si>
-    <t>0.06338105210438845</t>
-  </si>
-  <si>
-    <t>0.07316751020371741</t>
-  </si>
-  <si>
-    <t>0.08765972413702544</t>
+    <t>0.00010791967980829974</t>
+  </si>
+  <si>
+    <t>0.00011039997325312208</t>
+  </si>
+  <si>
+    <t>0.00011052534302482272</t>
+  </si>
+  <si>
+    <t>0.00012394825798645774</t>
+  </si>
+  <si>
+    <t>0.00013341300305468357</t>
+  </si>
+  <si>
+    <t>0.000135921825065123</t>
+  </si>
+  <si>
+    <t>0.00013593670415343288</t>
+  </si>
+  <si>
+    <t>0.00014089391449537914</t>
+  </si>
+  <si>
+    <t>0.0001521730370064979</t>
+  </si>
+  <si>
+    <t>0.00015478534785129066</t>
+  </si>
+  <si>
+    <t>0.00017624332184979023</t>
+  </si>
+  <si>
+    <t>0.0001768019200922207</t>
+  </si>
+  <si>
+    <t>0.00018678404226098842</t>
+  </si>
+  <si>
+    <t>0.00019136514908350865</t>
+  </si>
+  <si>
+    <t>0.00024139951598512677</t>
+  </si>
+  <si>
+    <t>0.00026911162425812213</t>
+  </si>
+  <si>
+    <t>0.0002825269062514095</t>
+  </si>
+  <si>
+    <t>0.00028446815161798955</t>
+  </si>
+  <si>
+    <t>0.00028608538568237617</t>
+  </si>
+  <si>
+    <t>0.00030882990002376623</t>
+  </si>
+  <si>
+    <t>0.00034999435994989065</t>
+  </si>
+  <si>
+    <t>0.00037472370591174424</t>
+  </si>
+  <si>
+    <t>0.00037854624774303616</t>
+  </si>
+  <si>
+    <t>0.0005076201934447272</t>
+  </si>
+  <si>
+    <t>0.0005759559987197094</t>
+  </si>
+  <si>
+    <t>0.000582293314136229</t>
+  </si>
+  <si>
+    <t>0.0006222659464916952</t>
+  </si>
+  <si>
+    <t>0.0008053512897516444</t>
+  </si>
+  <si>
+    <t>0.0008955491032011458</t>
+  </si>
+  <si>
+    <t>0.0009343706785920061</t>
+  </si>
+  <si>
+    <t>0.0009967688918952476</t>
+  </si>
+  <si>
+    <t>0.0010842976471724312</t>
+  </si>
+  <si>
+    <t>0.0012186322975319634</t>
+  </si>
+  <si>
+    <t>0.0014190885628456906</t>
+  </si>
+  <si>
+    <t>0.0014469087840113283</t>
+  </si>
+  <si>
+    <t>0.0014491212520376634</t>
+  </si>
+  <si>
+    <t>0.0014674594817959171</t>
+  </si>
+  <si>
+    <t>0.00163128693781488</t>
+  </si>
+  <si>
+    <t>0.0016925186713935426</t>
+  </si>
+  <si>
+    <t>0.0018137135946058535</t>
+  </si>
+  <si>
+    <t>0.0021106538860970565</t>
+  </si>
+  <si>
+    <t>0.0022138347773688538</t>
+  </si>
+  <si>
+    <t>0.0025163679888366673</t>
+  </si>
+  <si>
+    <t>0.002809861394547265</t>
+  </si>
+  <si>
+    <t>0.003019974351334551</t>
+  </si>
+  <si>
+    <t>0.003251422506766395</t>
+  </si>
+  <si>
+    <t>0.0035360309662528025</t>
+  </si>
+  <si>
+    <t>0.003750082673016792</t>
+  </si>
+  <si>
+    <t>0.003824097891313389</t>
+  </si>
+  <si>
+    <t>0.003909792660611477</t>
+  </si>
+  <si>
+    <t>0.0041319073389265715</t>
+  </si>
+  <si>
+    <t>0.004510317299145254</t>
+  </si>
+  <si>
+    <t>0.004523914814834442</t>
+  </si>
+  <si>
+    <t>0.004641604107933594</t>
+  </si>
+  <si>
+    <t>0.004740366459863871</t>
+  </si>
+  <si>
+    <t>0.004786251036795905</t>
+  </si>
+  <si>
+    <t>0.0048556464412190005</t>
+  </si>
+  <si>
+    <t>0.005128389150215745</t>
+  </si>
+  <si>
+    <t>0.005880954636039819</t>
+  </si>
+  <si>
+    <t>0.0059395739243510255</t>
+  </si>
+  <si>
+    <t>0.0063528253742027654</t>
+  </si>
+  <si>
+    <t>0.0071902010554176915</t>
+  </si>
+  <si>
+    <t>0.007345018168789084</t>
+  </si>
+  <si>
+    <t>0.00863720117467286</t>
+  </si>
+  <si>
+    <t>0.008908001439582622</t>
+  </si>
+  <si>
+    <t>0.00921827355717604</t>
+  </si>
+  <si>
+    <t>0.00942910613972303</t>
+  </si>
+  <si>
+    <t>0.009565322444713325</t>
+  </si>
+  <si>
+    <t>0.011384405468284505</t>
+  </si>
+  <si>
+    <t>0.011795052969343842</t>
+  </si>
+  <si>
+    <t>0.012277316560956358</t>
+  </si>
+  <si>
+    <t>0.013664483955594556</t>
+  </si>
+  <si>
+    <t>0.013747285420818264</t>
+  </si>
+  <si>
+    <t>0.013953479216572412</t>
+  </si>
+  <si>
+    <t>0.015296465858446254</t>
+  </si>
+  <si>
+    <t>0.015590203709032472</t>
+  </si>
+  <si>
+    <t>0.016218979364289184</t>
+  </si>
+  <si>
+    <t>0.016389067342837783</t>
+  </si>
+  <si>
+    <t>0.01687429657343649</t>
+  </si>
+  <si>
+    <t>0.01854148170643091</t>
+  </si>
+  <si>
+    <t>0.02104875153613527</t>
+  </si>
+  <si>
+    <t>0.021577129269715573</t>
+  </si>
+  <si>
+    <t>0.021857109838718157</t>
+  </si>
+  <si>
+    <t>0.022184903985646133</t>
+  </si>
+  <si>
+    <t>0.025909644245144504</t>
+  </si>
+  <si>
+    <t>0.027066496798223646</t>
+  </si>
+  <si>
+    <t>0.02814738455557069</t>
+  </si>
+  <si>
+    <t>0.02928063869017804</t>
+  </si>
+  <si>
+    <t>0.03001801057851834</t>
+  </si>
+  <si>
+    <t>0.03185583396420821</t>
+  </si>
+  <si>
+    <t>0.03578352249542942</t>
+  </si>
+  <si>
+    <t>0.055853738056076616</t>
+  </si>
+  <si>
+    <t>0.07019051243782701</t>
+  </si>
+  <si>
+    <t>0.1138471042790441</t>
+  </si>
+  <si>
+    <t>0.11794340701555578</t>
+  </si>
+  <si>
+    <t>0.00012159948872785391</t>
+  </si>
+  <si>
+    <t>0.0001226748699084776</t>
+  </si>
+  <si>
+    <t>0.0001249106330498471</t>
+  </si>
+  <si>
+    <t>0.00012680769073170517</t>
+  </si>
+  <si>
+    <t>0.00015048124739726478</t>
+  </si>
+  <si>
+    <t>0.00015334333910845048</t>
+  </si>
+  <si>
+    <t>0.00015658516112041567</t>
+  </si>
+  <si>
+    <t>0.00016462630508636616</t>
+  </si>
+  <si>
+    <t>0.00018519483464334564</t>
+  </si>
+  <si>
+    <t>0.0001910356601949871</t>
+  </si>
+  <si>
+    <t>0.0001994205594284445</t>
+  </si>
+  <si>
+    <t>0.00020633840106700228</t>
+  </si>
+  <si>
+    <t>0.00021154815110495677</t>
+  </si>
+  <si>
+    <t>0.00021301279492495832</t>
+  </si>
+  <si>
+    <t>0.00021563627009984658</t>
+  </si>
+  <si>
+    <t>0.00023711946201993822</t>
+  </si>
+  <si>
+    <t>0.00024246688575331154</t>
+  </si>
+  <si>
+    <t>0.00028945147997787546</t>
+  </si>
+  <si>
+    <t>0.00029293615871232246</t>
+  </si>
+  <si>
+    <t>0.00029371592815893047</t>
+  </si>
+  <si>
+    <t>0.00029696595229682343</t>
+  </si>
+  <si>
+    <t>0.0003126594443641216</t>
+  </si>
+  <si>
+    <t>0.00031565360077966337</t>
+  </si>
+  <si>
+    <t>0.0003479876266244842</t>
+  </si>
+  <si>
+    <t>0.0003663653347075803</t>
+  </si>
+  <si>
+    <t>0.0003884845145425362</t>
+  </si>
+  <si>
+    <t>0.0003944698388941572</t>
+  </si>
+  <si>
+    <t>0.00040153658902435026</t>
+  </si>
+  <si>
+    <t>0.000407316968010409</t>
+  </si>
+  <si>
+    <t>0.0004175115427151735</t>
+  </si>
+  <si>
+    <t>0.00045305135076195816</t>
+  </si>
+  <si>
+    <t>0.00047950206868749095</t>
+  </si>
+  <si>
+    <t>0.0005630648641368334</t>
+  </si>
+  <si>
+    <t>0.0005641791909548547</t>
+  </si>
+  <si>
+    <t>0.0005683268944681239</t>
+  </si>
+  <si>
+    <t>0.0005905238466309312</t>
+  </si>
+  <si>
+    <t>0.0005990482116878845</t>
+  </si>
+  <si>
+    <t>0.0006005617096758036</t>
+  </si>
+  <si>
+    <t>0.00060528968116815</t>
+  </si>
+  <si>
+    <t>0.0006079889347532667</t>
+  </si>
+  <si>
+    <t>0.0006168790889714578</t>
+  </si>
+  <si>
+    <t>0.000624618950462136</t>
+  </si>
+  <si>
+    <t>0.0007029623061123652</t>
+  </si>
+  <si>
+    <t>0.0007479102628703182</t>
+  </si>
+  <si>
+    <t>0.0007641715554135415</t>
+  </si>
+  <si>
+    <t>0.0007822071384957979</t>
+  </si>
+  <si>
+    <t>0.0008082591689065232</t>
+  </si>
+  <si>
+    <t>0.0008744842728397935</t>
+  </si>
+  <si>
+    <t>0.0010961800572465647</t>
+  </si>
+  <si>
+    <t>0.0011519211135065806</t>
+  </si>
+  <si>
+    <t>0.0012043535513784746</t>
+  </si>
+  <si>
+    <t>0.0012162245334273623</t>
+  </si>
+  <si>
+    <t>0.0012573155498998955</t>
+  </si>
+  <si>
+    <t>0.001311210305078956</t>
+  </si>
+  <si>
+    <t>0.001326629265139002</t>
+  </si>
+  <si>
+    <t>0.0013414097775516789</t>
+  </si>
+  <si>
+    <t>0.0014208400532925284</t>
+  </si>
+  <si>
+    <t>0.0014843884716282637</t>
+  </si>
+  <si>
+    <t>0.0015361162555855257</t>
+  </si>
+  <si>
+    <t>0.001730406079661322</t>
+  </si>
+  <si>
+    <t>0.001775772279798053</t>
+  </si>
+  <si>
+    <t>0.0017830958963502286</t>
+  </si>
+  <si>
+    <t>0.0019458129093216426</t>
+  </si>
+  <si>
+    <t>0.002197200921790961</t>
+  </si>
+  <si>
+    <t>0.0031172184446222684</t>
+  </si>
+  <si>
+    <t>0.0031481768334243993</t>
+  </si>
+  <si>
+    <t>0.003246866201137377</t>
+  </si>
+  <si>
+    <t>0.003511347878104979</t>
+  </si>
+  <si>
+    <t>0.003534920984137877</t>
+  </si>
+  <si>
+    <t>0.003638918276535236</t>
+  </si>
+  <si>
+    <t>0.0038365992089791816</t>
+  </si>
+  <si>
+    <t>0.0038574203098631498</t>
+  </si>
+  <si>
+    <t>0.003892662834033094</t>
+  </si>
+  <si>
+    <t>0.004007447779665567</t>
+  </si>
+  <si>
+    <t>0.004100376846665722</t>
+  </si>
+  <si>
+    <t>0.00444530981656353</t>
+  </si>
+  <si>
+    <t>0.004496978548473976</t>
+  </si>
+  <si>
+    <t>0.004863371018690239</t>
+  </si>
+  <si>
+    <t>0.005470676295776108</t>
+  </si>
+  <si>
+    <t>0.006549001273471045</t>
+  </si>
+  <si>
+    <t>0.006686020957952926</t>
+  </si>
+  <si>
+    <t>0.007800988546493573</t>
+  </si>
+  <si>
+    <t>0.008130716666190535</t>
+  </si>
+  <si>
+    <t>0.01020870716196334</t>
+  </si>
+  <si>
+    <t>0.01310667407183872</t>
+  </si>
+  <si>
+    <t>0.013547717877181103</t>
+  </si>
+  <si>
+    <t>0.017798282644846668</t>
+  </si>
+  <si>
+    <t>0.022735199201021197</t>
+  </si>
+  <si>
+    <t>0.023530533735607304</t>
+  </si>
+  <si>
+    <t>0.02599192519520646</t>
+  </si>
+  <si>
+    <t>0.02669941851819107</t>
+  </si>
+  <si>
+    <t>0.02854749230877556</t>
+  </si>
+  <si>
+    <t>0.02928748233291132</t>
+  </si>
+  <si>
+    <t>0.029302181133024706</t>
+  </si>
+  <si>
+    <t>0.04006693422938794</t>
+  </si>
+  <si>
+    <t>0.05108842845794201</t>
+  </si>
+  <si>
+    <t>0.059683691479076734</t>
+  </si>
+  <si>
+    <t>0.08359701129800916</t>
+  </si>
+  <si>
+    <t>0.11322335067140475</t>
+  </si>
+  <si>
+    <t>0.129979415689768</t>
+  </si>
+  <si>
+    <t>0.14952278206805272</t>
+  </si>
+  <si>
+    <t>0.00010534593780944463</t>
+  </si>
+  <si>
+    <t>0.00011701181739239709</t>
+  </si>
+  <si>
+    <t>0.00011751580837798234</t>
+  </si>
+  <si>
+    <t>0.000122073160347748</t>
+  </si>
+  <si>
+    <t>0.00014814116812457065</t>
+  </si>
+  <si>
+    <t>0.00014827804887728027</t>
+  </si>
+  <si>
+    <t>0.00018189796039699672</t>
+  </si>
+  <si>
+    <t>0.00019012533747993235</t>
+  </si>
+  <si>
+    <t>0.00020123069036917168</t>
+  </si>
+  <si>
+    <t>0.0002536571576167183</t>
+  </si>
+  <si>
+    <t>0.000254981662780668</t>
+  </si>
+  <si>
+    <t>0.00028233066707353434</t>
+  </si>
+  <si>
+    <t>0.0002959776913513257</t>
+  </si>
+  <si>
+    <t>0.00046052591757274526</t>
+  </si>
+  <si>
+    <t>0.0005076822828769696</t>
+  </si>
+  <si>
+    <t>0.0005501316953489301</t>
+  </si>
+  <si>
+    <t>0.0006104693344948185</t>
+  </si>
+  <si>
+    <t>0.0006568870908967487</t>
+  </si>
+  <si>
+    <t>0.0006905066431634878</t>
+  </si>
+  <si>
+    <t>0.0007059929764851477</t>
+  </si>
+  <si>
+    <t>0.0007432318662953653</t>
+  </si>
+  <si>
+    <t>0.0007746657081756989</t>
+  </si>
+  <si>
+    <t>0.0007820641306541503</t>
+  </si>
+  <si>
+    <t>0.0007824093092020158</t>
+  </si>
+  <si>
+    <t>0.0008172560093203337</t>
+  </si>
+  <si>
+    <t>0.0008827456964061088</t>
+  </si>
+  <si>
+    <t>0.0009742657483789447</t>
+  </si>
+  <si>
+    <t>0.0010231903770040883</t>
+  </si>
+  <si>
+    <t>0.0011178653956738427</t>
+  </si>
+  <si>
+    <t>0.001144233187066814</t>
+  </si>
+  <si>
+    <t>0.001304857596113404</t>
+  </si>
+  <si>
+    <t>0.0014050159624874922</t>
+  </si>
+  <si>
+    <t>0.0014556880853899682</t>
+  </si>
+  <si>
+    <t>0.0015149170375419784</t>
+  </si>
+  <si>
+    <t>0.001614429483567414</t>
+  </si>
+  <si>
+    <t>0.0016557789371172372</t>
+  </si>
+  <si>
+    <t>0.0020445554428744446</t>
+  </si>
+  <si>
+    <t>0.0024241629452800327</t>
+  </si>
+  <si>
+    <t>0.003003705435568944</t>
+  </si>
+  <si>
+    <t>0.0031699214535529053</t>
+  </si>
+  <si>
+    <t>0.003836631868716856</t>
+  </si>
+  <si>
+    <t>0.004670026593608678</t>
+  </si>
+  <si>
+    <t>0.004818927755804104</t>
+  </si>
+  <si>
+    <t>0.005159932611264964</t>
+  </si>
+  <si>
+    <t>0.005390879352648895</t>
+  </si>
+  <si>
+    <t>0.0054158795300992876</t>
+  </si>
+  <si>
+    <t>0.006632769826924041</t>
+  </si>
+  <si>
+    <t>0.0068568270046143786</t>
+  </si>
+  <si>
+    <t>0.007005040885761249</t>
+  </si>
+  <si>
+    <t>0.0074233295943183395</t>
+  </si>
+  <si>
+    <t>0.007722663015188882</t>
+  </si>
+  <si>
+    <t>0.00876747298729251</t>
+  </si>
+  <si>
+    <t>0.008834961356870815</t>
+  </si>
+  <si>
+    <t>0.00885754226874848</t>
+  </si>
+  <si>
+    <t>0.010466063116653997</t>
+  </si>
+  <si>
+    <t>0.010806494721749044</t>
+  </si>
+  <si>
+    <t>0.012785657043760619</t>
+  </si>
+  <si>
+    <t>0.013971331367350261</t>
+  </si>
+  <si>
+    <t>0.015208625590599247</t>
+  </si>
+  <si>
+    <t>0.01626175385858714</t>
+  </si>
+  <si>
+    <t>0.016715760821007924</t>
+  </si>
+  <si>
+    <t>0.017151635096895733</t>
+  </si>
+  <si>
+    <t>0.01819198501784084</t>
+  </si>
+  <si>
+    <t>0.019160451897209142</t>
+  </si>
+  <si>
+    <t>0.0210145804833526</t>
+  </si>
+  <si>
+    <t>0.02524238977407262</t>
+  </si>
+  <si>
+    <t>0.02608334081546967</t>
+  </si>
+  <si>
+    <t>0.026134493545513164</t>
+  </si>
+  <si>
+    <t>0.02660729981385053</t>
+  </si>
+  <si>
+    <t>0.026658043839510533</t>
+  </si>
+  <si>
+    <t>0.027030249847841338</t>
+  </si>
+  <si>
+    <t>0.028726640914025072</t>
+  </si>
+  <si>
+    <t>0.04016399035518474</t>
+  </si>
+  <si>
+    <t>0.04373823052400842</t>
+  </si>
+  <si>
+    <t>0.060886320596405155</t>
+  </si>
+  <si>
+    <t>0.06380721901357507</t>
+  </si>
+  <si>
+    <t>0.06984610062547919</t>
+  </si>
+  <si>
+    <t>0.07189534746418542</t>
+  </si>
+  <si>
+    <t>0.07900120010851394</t>
+  </si>
+  <si>
+    <t>0.08447880630381106</t>
   </si>
 </sst>
 </file>
@@ -2600,8 +2366,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A713DF-5F5D-4CC6-A332-86D7C95B8F88}">
-  <dimension ref="A1:B176"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C0CAFB5-8652-4188-BEA7-11D52080C498}">
+  <dimension ref="A1:B130"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="72.85546875" bestFit="1" customWidth="1"/>
@@ -3308,712 +3074,344 @@
       <c r="A88" t="s">
         <v>174</v>
       </c>
-      <c r="B88" t="s">
-        <v>175</v>
+      <c r="B88" s="1">
+        <v>96206107024.004105</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>176</v>
-      </c>
-      <c r="B89" t="s">
-        <v>177</v>
+        <v>175</v>
+      </c>
+      <c r="B89" s="1">
+        <v>92433184485.223007</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>178</v>
-      </c>
-      <c r="B90" t="s">
-        <v>179</v>
+        <v>176</v>
+      </c>
+      <c r="B90" s="1">
+        <v>85664570882.614502</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>180</v>
-      </c>
-      <c r="B91" t="s">
-        <v>181</v>
+        <v>177</v>
+      </c>
+      <c r="B91" s="1">
+        <v>84492561218.474197</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>182</v>
-      </c>
-      <c r="B92" t="s">
-        <v>183</v>
+        <v>178</v>
+      </c>
+      <c r="B92" s="1">
+        <v>80063417741.5448</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>184</v>
-      </c>
-      <c r="B93" t="s">
-        <v>185</v>
+        <v>179</v>
+      </c>
+      <c r="B93" s="1">
+        <v>77203871262.799103</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B94" s="1">
-        <v>85481712268.796799</v>
+        <v>745896391.28357995</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B95" s="1">
-        <v>81951954990.251907</v>
+        <v>74223126434.193405</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B96" s="1">
-        <v>79227651309.293106</v>
+        <v>73209409143.5224</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B97" s="1">
-        <v>75963456792.845901</v>
+        <v>71024751800.129593</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B98" s="1">
-        <v>69167269590.280106</v>
+        <v>58964071832.408302</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B99" s="1">
-        <v>6716771192.6679401</v>
+        <v>553767783141.80603</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B100" s="1">
-        <v>65456809065.893204</v>
+        <v>52855264422.366402</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B101" s="1">
-        <v>60921473285.133698</v>
+        <v>522425217457.86102</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B102" s="1">
-        <v>59846028379.8405</v>
+        <v>43183034549.546997</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B103" s="1">
-        <v>592462100998.39697</v>
+        <v>31434138431.647301</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B104" s="1">
-        <v>57977156703.007103</v>
+        <v>281594183693.21002</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B105" s="1">
-        <v>479639105996.53497</v>
+        <v>277913549382.76202</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B106" s="1">
-        <v>47303941388.924797</v>
+        <v>2040593814.1382201</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B107" s="1">
-        <v>459978358161.94397</v>
+        <v>198235052.25523001</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B108" s="1">
-        <v>41883930809.674103</v>
+        <v>166498049527.72</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B109" s="1">
-        <v>41163635330.969002</v>
+        <v>143575604831.98801</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B110" s="1">
-        <v>411374739893.94598</v>
+        <v>13346911096.589899</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B111" s="1">
-        <v>41073496319.180099</v>
+        <v>9640989869.3558102</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B112" s="1">
-        <v>40903437045.381401</v>
+        <v>8876873065.3206291</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B113" s="1">
-        <v>325233325672.242</v>
+        <v>8458244396.8111496</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B114" s="1">
-        <v>2976854541.8685699</v>
+        <v>7188269136.1148796</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B115" s="1">
-        <v>29417468335.584202</v>
+        <v>6944352947.3158102</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B116" s="1">
-        <v>29393479884.3055</v>
+        <v>5671801643.2190399</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B117" s="1">
-        <v>288029142698.15002</v>
+        <v>5468981243.3794098</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B118" s="1">
-        <v>283200129583.88098</v>
+        <v>2678348573.8322802</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B119" s="1">
-        <v>25498173539.345901</v>
+        <v>26210927067.4856</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B120" s="1">
-        <v>246249433230.36499</v>
+        <v>16244961429.042</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B121" s="1">
-        <v>21750372310.677799</v>
+        <v>15648542065.4438</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B122" s="1">
-        <v>21730506331.979401</v>
+        <v>11923496866.6821</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B123" s="1">
-        <v>177546616958.45801</v>
+        <v>11409912928.621201</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B124" s="1">
-        <v>171946844700.11401</v>
+        <v>10377977018.8652</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B125" s="1">
-        <v>163900239878.755</v>
+        <v>861442079.47044694</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B126" s="1">
-        <v>158021388675.271</v>
+        <v>491324033.71791899</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B127" s="1">
-        <v>143928303079.43701</v>
+        <v>75705007.232922494</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>220</v>
-      </c>
-      <c r="B128" s="1">
-        <v>140002706898.776</v>
+        <v>214</v>
+      </c>
+      <c r="B128" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>221</v>
-      </c>
-      <c r="B129" s="1">
-        <v>10039377639.283199</v>
+        <v>216</v>
+      </c>
+      <c r="B129" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>222</v>
-      </c>
-      <c r="B130" s="1">
-        <v>9539192556.1344604</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>223</v>
-      </c>
-      <c r="B131" s="1">
-        <v>9354545697.3028393</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>224</v>
-      </c>
-      <c r="B132" s="1">
-        <v>87309852.656084999</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>225</v>
-      </c>
-      <c r="B133" s="1">
-        <v>8235924685.1014795</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>226</v>
-      </c>
-      <c r="B134" s="1">
-        <v>8195106697.80618</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>227</v>
-      </c>
-      <c r="B135" s="1">
-        <v>8140181247.5086699</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>228</v>
-      </c>
-      <c r="B136" s="1">
-        <v>8023869381.5510302</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>229</v>
-      </c>
-      <c r="B137" s="1">
-        <v>7036873599.8295698</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>230</v>
-      </c>
-      <c r="B138" s="1">
-        <v>5587880717.4033098</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>231</v>
-      </c>
-      <c r="B139" s="1">
-        <v>516632917.229186</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>232</v>
-      </c>
-      <c r="B140" s="1">
-        <v>4304498234.3765898</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>233</v>
-      </c>
-      <c r="B141" s="1">
-        <v>36570571904.787201</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>234</v>
-      </c>
-      <c r="B142" s="1">
-        <v>27449826680.864899</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>235</v>
-      </c>
-      <c r="B143" s="1">
-        <v>26253985830.162399</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>236</v>
-      </c>
-      <c r="B144" s="1">
-        <v>25563209806.625801</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>237</v>
-      </c>
-      <c r="B145" s="1">
-        <v>2389313701.6526299</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>238</v>
-      </c>
-      <c r="B146" s="1">
-        <v>18004379039.860802</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>239</v>
-      </c>
-      <c r="B147" s="1">
-        <v>168997023.69512901</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>240</v>
-      </c>
-      <c r="B148" s="1">
-        <v>16698009575.054001</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>241</v>
-      </c>
-      <c r="B149" s="1">
-        <v>134249386.761922</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>242</v>
-      </c>
-      <c r="B150" s="1">
-        <v>912704.06672230002</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>243</v>
-      </c>
-      <c r="B151" s="1">
-        <v>896894596.03820598</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>244</v>
-      </c>
-      <c r="B152" s="1">
-        <v>681510901.03215206</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>245</v>
-      </c>
-      <c r="B153" s="1">
-        <v>681280056.17244101</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>246</v>
-      </c>
-      <c r="B154" s="1">
-        <v>649133851.62160397</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>247</v>
-      </c>
-      <c r="B155" s="1">
-        <v>570815380.18840897</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>248</v>
-      </c>
-      <c r="B156" s="1">
-        <v>2981893520.8289099</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>249</v>
-      </c>
-      <c r="B157" s="1">
-        <v>272357810.42415601</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>250</v>
-      </c>
-      <c r="B158" s="1">
-        <v>2532827904.6949801</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>251</v>
-      </c>
-      <c r="B159" s="1">
-        <v>182954201.323273</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>252</v>
-      </c>
-      <c r="B160" s="1">
-        <v>1492125585.97683</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>253</v>
-      </c>
-      <c r="B161" s="1">
-        <v>1240509657.75806</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>254</v>
-      </c>
-      <c r="B162" s="1">
-        <v>91844439.652217001</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>255</v>
-      </c>
-      <c r="B163" s="1">
-        <v>29720342.402381901</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>256</v>
-      </c>
-      <c r="B164" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>258</v>
-      </c>
-      <c r="B165" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>259</v>
-      </c>
-      <c r="B166" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>260</v>
-      </c>
-      <c r="B167" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>261</v>
-      </c>
-      <c r="B168" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>262</v>
-      </c>
-      <c r="B169" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>263</v>
-      </c>
-      <c r="B170" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>264</v>
-      </c>
-      <c r="B171" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>265</v>
-      </c>
-      <c r="B172" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>266</v>
-      </c>
-      <c r="B173" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>267</v>
-      </c>
-      <c r="B174" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>268</v>
-      </c>
-      <c r="B175" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>269</v>
-      </c>
-      <c r="B176" t="s">
-        <v>257</v>
+        <v>217</v>
+      </c>
+      <c r="B130" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -4022,8 +3420,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1B07F5-D03D-42DB-A53C-40BBE0EF762E}">
-  <dimension ref="A1:B176"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{046253C1-162C-4094-B699-95DBB47C22CC}">
+  <dimension ref="A1:B130"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="72.85546875" bestFit="1" customWidth="1"/>
@@ -4040,50 +3438,50 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>369</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>368</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>367</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>366</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>365</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>364</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4091,167 +3489,167 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>363</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>362</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>361</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>360</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>359</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>358</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>357</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>356</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>355</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>354</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>353</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>352</v>
+        <v>295</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>351</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>350</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>349</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B23" t="s">
-        <v>348</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>347</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>346</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>345</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>344</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B28" t="s">
-        <v>343</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -4259,79 +3657,79 @@
         <v>60</v>
       </c>
       <c r="B29" t="s">
-        <v>342</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B30" t="s">
-        <v>341</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>340</v>
+        <v>283</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>339</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B33" t="s">
-        <v>338</v>
+        <v>281</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B34" t="s">
-        <v>337</v>
+        <v>280</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>336</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>335</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>334</v>
+        <v>277</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B38" t="s">
-        <v>333</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -4339,111 +3737,111 @@
         <v>72</v>
       </c>
       <c r="B39" t="s">
-        <v>332</v>
+        <v>275</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="B40" t="s">
-        <v>331</v>
+        <v>274</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>330</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
-        <v>329</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="B43" t="s">
-        <v>328</v>
+        <v>271</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B44" t="s">
-        <v>327</v>
+        <v>270</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B45" t="s">
-        <v>326</v>
+        <v>269</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>325</v>
+        <v>268</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="B47" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B48" t="s">
-        <v>323</v>
+        <v>266</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B49" t="s">
-        <v>322</v>
+        <v>265</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B50" t="s">
-        <v>321</v>
+        <v>264</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="B51" t="s">
-        <v>320</v>
+        <v>263</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B52" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -4451,39 +3849,39 @@
         <v>108</v>
       </c>
       <c r="B53" t="s">
-        <v>318</v>
+        <v>261</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B54" t="s">
-        <v>317</v>
+        <v>260</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="B55" t="s">
-        <v>316</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B56" t="s">
-        <v>315</v>
+        <v>258</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B57" t="s">
-        <v>314</v>
+        <v>257</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -4491,23 +3889,23 @@
         <v>130</v>
       </c>
       <c r="B58" t="s">
-        <v>313</v>
+        <v>256</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B59" t="s">
-        <v>312</v>
+        <v>255</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="B60" t="s">
-        <v>311</v>
+        <v>254</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -4515,7 +3913,7 @@
         <v>118</v>
       </c>
       <c r="B61" t="s">
-        <v>310</v>
+        <v>253</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -4523,15 +3921,15 @@
         <v>134</v>
       </c>
       <c r="B62" t="s">
-        <v>309</v>
+        <v>252</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="B63" t="s">
-        <v>308</v>
+        <v>251</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -4539,47 +3937,47 @@
         <v>110</v>
       </c>
       <c r="B64" t="s">
-        <v>307</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="B65" t="s">
-        <v>306</v>
+        <v>249</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B66" t="s">
-        <v>305</v>
+        <v>248</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="B67" t="s">
-        <v>304</v>
+        <v>247</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B68" t="s">
-        <v>303</v>
+        <v>246</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B69" t="s">
-        <v>302</v>
+        <v>245</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -4587,855 +3985,487 @@
         <v>136</v>
       </c>
       <c r="B70" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B71" t="s">
-        <v>300</v>
+        <v>243</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="B72" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="B73" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>209</v>
+        <v>144</v>
       </c>
       <c r="B74" t="s">
-        <v>297</v>
+        <v>240</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="B75" t="s">
-        <v>296</v>
+        <v>239</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B76" t="s">
-        <v>295</v>
+        <v>238</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>207</v>
+        <v>154</v>
       </c>
       <c r="B77" t="s">
-        <v>294</v>
+        <v>237</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B78" t="s">
-        <v>293</v>
+        <v>236</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="B79" t="s">
-        <v>292</v>
+        <v>235</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B80" t="s">
-        <v>291</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="B81" t="s">
-        <v>290</v>
+        <v>233</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B82" t="s">
-        <v>289</v>
+        <v>232</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B83" t="s">
-        <v>288</v>
+        <v>231</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="B84" t="s">
-        <v>287</v>
+        <v>230</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B85" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="B86" t="s">
-        <v>285</v>
+        <v>228</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="B87" t="s">
-        <v>284</v>
+        <v>227</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B88" t="s">
-        <v>283</v>
+        <v>226</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="B89" t="s">
-        <v>282</v>
+        <v>225</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B90" t="s">
-        <v>281</v>
+        <v>224</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B91" t="s">
-        <v>280</v>
+        <v>223</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>231</v>
+        <v>172</v>
       </c>
       <c r="B92" t="s">
-        <v>279</v>
+        <v>222</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="B93" t="s">
-        <v>278</v>
+        <v>221</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B94" t="s">
-        <v>277</v>
+        <v>220</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B95" t="s">
-        <v>276</v>
+        <v>219</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B96" t="s">
-        <v>275</v>
+        <v>218</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>192</v>
-      </c>
-      <c r="B97" t="s">
-        <v>274</v>
+        <v>176</v>
+      </c>
+      <c r="B97" s="1">
+        <v>99186024529.910202</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>236</v>
-      </c>
-      <c r="B98" t="s">
-        <v>273</v>
+        <v>196</v>
+      </c>
+      <c r="B98" s="1">
+        <v>84631273019.735001</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>205</v>
-      </c>
-      <c r="B99" t="s">
-        <v>272</v>
+        <v>178</v>
+      </c>
+      <c r="B99" s="1">
+        <v>77365474971.202103</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>146</v>
-      </c>
-      <c r="B100" t="s">
-        <v>271</v>
+        <v>183</v>
+      </c>
+      <c r="B100" s="1">
+        <v>75237755233.421204</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>186</v>
-      </c>
-      <c r="B101" t="s">
-        <v>270</v>
+        <v>189</v>
+      </c>
+      <c r="B101" s="1">
+        <v>67684123439.125298</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B102" s="1">
-        <v>98726466973.436493</v>
+        <v>54094178246.705597</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B103" s="1">
-        <v>91330545329.869293</v>
+        <v>526313007435.79498</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="B104" s="1">
-        <v>84988257148.897705</v>
+        <v>523031118346.56897</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="B105" s="1">
-        <v>84544175941.880905</v>
+        <v>50394952045.5597</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="B106" s="1">
-        <v>78205870517.929993</v>
+        <v>43631298068.877403</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="B107" s="1">
-        <v>72119459283.336395</v>
+        <v>425517784430.16901</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="B108" s="1">
-        <v>72025179299.553207</v>
+        <v>36324412009.250397</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B109" s="1">
-        <v>7124963681.2905703</v>
+        <v>33402247175.411098</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B110" s="1">
-        <v>71111501782.603607</v>
+        <v>31800874874.0354</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B111" s="1">
-        <v>61295269953.587502</v>
+        <v>297724244479.35797</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>210</v>
+        <v>146</v>
       </c>
       <c r="B112" s="1">
-        <v>60768607499.398399</v>
+        <v>287772408680.13</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B113" s="1">
-        <v>58295282139.505997</v>
+        <v>2459314353.32758</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>142</v>
+        <v>195</v>
       </c>
       <c r="B114" s="1">
-        <v>56858873222.026299</v>
+        <v>227391848286.20499</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="B115" s="1">
-        <v>56215646378.597198</v>
+        <v>168124527399.98801</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="B116" s="1">
-        <v>551815265010.91699</v>
+        <v>135795194046.82899</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="B117" s="1">
-        <v>53669740103.814003</v>
+        <v>133131319963.30901</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="B118" s="1">
-        <v>53576453435.112198</v>
+        <v>120496350217.821</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B119" s="1">
-        <v>50874517061.774597</v>
+        <v>120474189861.10699</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="B120" s="1">
-        <v>485443518422.97498</v>
+        <v>8924127545.3865891</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B121" s="1">
-        <v>482977450695.034</v>
+        <v>8646866282.1465607</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B122" s="1">
-        <v>466913268048.41699</v>
+        <v>66599313516.564697</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>164</v>
+        <v>206</v>
       </c>
       <c r="B123" s="1">
-        <v>420777031007.41302</v>
+        <v>6086954567.8790703</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="B124" s="1">
-        <v>36140690615.573799</v>
+        <v>5520041827.2758904</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B125" s="1">
-        <v>350524717992.06598</v>
+        <v>284615831.95757103</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B126" s="1">
-        <v>350148655889.03101</v>
+        <v>21912831805.299702</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="B127" s="1">
-        <v>343402503599.086</v>
+        <v>20699195790.266998</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B128" s="1">
-        <v>330258020709.67603</v>
+        <v>15252436878.9764</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B129" s="1">
-        <v>311033835874.36603</v>
+        <v>728561502.26522601</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="B130" s="1">
-        <v>30520989152.260899</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>233</v>
-      </c>
-      <c r="B131" s="1">
-        <v>297950719361.29602</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>256</v>
-      </c>
-      <c r="B132" s="1">
-        <v>29035340959.0914</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>206</v>
-      </c>
-      <c r="B133" s="1">
-        <v>28976102987.821201</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>225</v>
-      </c>
-      <c r="B134" s="1">
-        <v>25940200687.115002</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>197</v>
-      </c>
-      <c r="B135" s="1">
-        <v>25247235983.006599</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>251</v>
-      </c>
-      <c r="B136" s="1">
-        <v>23662107454.998001</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>203</v>
-      </c>
-      <c r="B137" s="1">
-        <v>235246769271.664</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>215</v>
-      </c>
-      <c r="B138" s="1">
-        <v>23276044981.393299</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>188</v>
-      </c>
-      <c r="B139" s="1">
-        <v>231568822400.60901</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>217</v>
-      </c>
-      <c r="B140" s="1">
-        <v>202263181314.66199</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>219</v>
-      </c>
-      <c r="B141" s="1">
-        <v>179476361476.67499</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>232</v>
-      </c>
-      <c r="B142" s="1">
-        <v>1756323291.89063</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>234</v>
-      </c>
-      <c r="B143" s="1">
-        <v>16995117288.2337</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>224</v>
-      </c>
-      <c r="B144" s="1">
-        <v>157744344272.65399</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>265</v>
-      </c>
-      <c r="B145" s="1">
-        <v>13994594870.9519</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>263</v>
-      </c>
-      <c r="B146" s="1">
-        <v>132065502865.771</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>230</v>
-      </c>
-      <c r="B147" s="1">
-        <v>127206182165.74001</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>247</v>
-      </c>
-      <c r="B148" s="1">
-        <v>118480005390.28</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>264</v>
-      </c>
-      <c r="B149" s="1">
-        <v>112863438566.024</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>269</v>
-      </c>
-      <c r="B150" s="1">
-        <v>105481461089.173</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>198</v>
-      </c>
-      <c r="B151" s="1">
-        <v>9599720978.9881496</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>268</v>
-      </c>
-      <c r="B152" s="1">
-        <v>8681176356.6689205</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>240</v>
-      </c>
-      <c r="B153" s="1">
-        <v>7440289104.2675896</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>238</v>
-      </c>
-      <c r="B154" s="1">
-        <v>6575924162.45012</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>246</v>
-      </c>
-      <c r="B155" s="1">
-        <v>6402281313.9864197</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>237</v>
-      </c>
-      <c r="B156" s="1">
-        <v>4699749784.0174303</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>239</v>
-      </c>
-      <c r="B157" s="1">
-        <v>4516052210.9091902</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>241</v>
-      </c>
-      <c r="B158" s="1">
-        <v>29031192487.797901</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>244</v>
-      </c>
-      <c r="B159" s="1">
-        <v>21705608717.130299</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>242</v>
-      </c>
-      <c r="B160" s="1">
-        <v>21445392519.546398</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>248</v>
-      </c>
-      <c r="B161" s="1">
-        <v>2102571128.7402599</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>243</v>
-      </c>
-      <c r="B162" s="1">
-        <v>18155786591.638699</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>261</v>
-      </c>
-      <c r="B163" s="1">
-        <v>14316787280.651501</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>262</v>
-      </c>
-      <c r="B164" s="1">
-        <v>10654652151.9825</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>252</v>
-      </c>
-      <c r="B165" s="1">
-        <v>720445724.31379402</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>250</v>
-      </c>
-      <c r="B166" s="1">
-        <v>433251160.92207301</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>266</v>
-      </c>
-      <c r="B167" s="1">
-        <v>195008874.47562501</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>245</v>
-      </c>
-      <c r="B168" s="1">
-        <v>1623649983.0903101</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>255</v>
-      </c>
-      <c r="B169" s="1">
-        <v>1447868008.7105701</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>253</v>
-      </c>
-      <c r="B170" s="1">
-        <v>1183711265.79707</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>267</v>
-      </c>
-      <c r="B171" s="1">
-        <v>71294017.828717798</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>249</v>
-      </c>
-      <c r="B172" s="1">
-        <v>486017745.81702203</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>260</v>
-      </c>
-      <c r="B173" s="1">
-        <v>16017630.342374099</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>254</v>
-      </c>
-      <c r="B174" s="1">
-        <v>4129313.89592337</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>258</v>
-      </c>
-      <c r="B175" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>259</v>
-      </c>
-      <c r="B176" t="s">
-        <v>257</v>
+        <v>1784420621.33793</v>
       </c>
     </row>
   </sheetData>
@@ -5444,8 +4474,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F205EB90-6D65-466F-AAC4-4E4AE0FCCE6A}">
-  <dimension ref="A1:B176"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89DC966A-39F2-4431-812D-21AAD9F5599D}">
+  <dimension ref="A1:B130"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="72.85546875" bestFit="1" customWidth="1"/>
@@ -5462,10 +4492,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>489</v>
+        <v>413</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -5473,175 +4503,175 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>488</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>487</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>486</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>485</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>484</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>483</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>482</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>481</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>480</v>
+        <v>404</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>479</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>478</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>477</v>
+        <v>401</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>476</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>475</v>
+        <v>399</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B17" t="s">
-        <v>474</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>473</v>
+        <v>397</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>472</v>
+        <v>396</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>471</v>
+        <v>395</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
-        <v>470</v>
+        <v>394</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>469</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>468</v>
+        <v>392</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>467</v>
+        <v>391</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -5649,39 +4679,39 @@
         <v>78</v>
       </c>
       <c r="B25" t="s">
-        <v>466</v>
+        <v>390</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>465</v>
+        <v>389</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
-        <v>464</v>
+        <v>388</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>463</v>
+        <v>387</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>462</v>
+        <v>386</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -5689,1175 +4719,807 @@
         <v>102</v>
       </c>
       <c r="B30" t="s">
-        <v>461</v>
+        <v>385</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>460</v>
+        <v>384</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B32" t="s">
-        <v>459</v>
+        <v>383</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="B33" t="s">
-        <v>458</v>
+        <v>382</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B34" t="s">
-        <v>457</v>
+        <v>381</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="B35" t="s">
-        <v>456</v>
+        <v>380</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="B36" t="s">
-        <v>455</v>
+        <v>379</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="B37" t="s">
-        <v>454</v>
+        <v>378</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="B38" t="s">
-        <v>453</v>
+        <v>377</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>190</v>
       </c>
       <c r="B39" t="s">
-        <v>452</v>
+        <v>376</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>116</v>
+        <v>181</v>
       </c>
       <c r="B40" t="s">
-        <v>451</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>450</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
-        <v>449</v>
+        <v>373</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="B43" t="s">
-        <v>448</v>
+        <v>372</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="B44" t="s">
-        <v>447</v>
+        <v>371</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B45" t="s">
-        <v>446</v>
+        <v>370</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="B46" t="s">
-        <v>445</v>
+        <v>369</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>86</v>
+        <v>208</v>
       </c>
       <c r="B47" t="s">
-        <v>444</v>
+        <v>368</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="B48" t="s">
-        <v>443</v>
+        <v>367</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="B49" t="s">
-        <v>442</v>
+        <v>366</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="B50" t="s">
-        <v>441</v>
+        <v>365</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B51" t="s">
-        <v>440</v>
+        <v>364</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>122</v>
+        <v>38</v>
       </c>
       <c r="B52" t="s">
-        <v>439</v>
+        <v>363</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="B53" t="s">
-        <v>438</v>
+        <v>362</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="B54" t="s">
-        <v>437</v>
+        <v>361</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>132</v>
+        <v>184</v>
       </c>
       <c r="B55" t="s">
-        <v>436</v>
+        <v>360</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="B56" t="s">
-        <v>435</v>
+        <v>359</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>126</v>
+        <v>186</v>
       </c>
       <c r="B57" t="s">
-        <v>434</v>
+        <v>358</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B58" t="s">
-        <v>433</v>
+        <v>357</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="B59" t="s">
-        <v>432</v>
+        <v>356</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>226</v>
+        <v>185</v>
       </c>
       <c r="B60" t="s">
-        <v>431</v>
+        <v>355</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>229</v>
+        <v>94</v>
       </c>
       <c r="B61" t="s">
-        <v>430</v>
+        <v>354</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>235</v>
+        <v>76</v>
       </c>
       <c r="B62" t="s">
-        <v>429</v>
+        <v>353</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B63" t="s">
-        <v>428</v>
+        <v>352</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="B64" t="s">
-        <v>427</v>
+        <v>351</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>90</v>
+        <v>174</v>
       </c>
       <c r="B65" t="s">
-        <v>426</v>
+        <v>350</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="B66" t="s">
-        <v>425</v>
+        <v>349</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="B67" t="s">
-        <v>424</v>
+        <v>348</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="B68" t="s">
-        <v>423</v>
+        <v>347</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="B69" t="s">
-        <v>422</v>
+        <v>346</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="B70" t="s">
-        <v>421</v>
+        <v>345</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B71" t="s">
-        <v>420</v>
+        <v>344</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>221</v>
+        <v>116</v>
       </c>
       <c r="B72" t="s">
-        <v>419</v>
+        <v>343</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>146</v>
+        <v>214</v>
       </c>
       <c r="B73" t="s">
-        <v>418</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B74" t="s">
-        <v>417</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>106</v>
+        <v>194</v>
       </c>
       <c r="B75" t="s">
-        <v>416</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>104</v>
+        <v>197</v>
       </c>
       <c r="B76" t="s">
-        <v>415</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>142</v>
+        <v>199</v>
       </c>
       <c r="B77" t="s">
-        <v>414</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>256</v>
+        <v>108</v>
       </c>
       <c r="B78" t="s">
-        <v>413</v>
+        <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B79" t="s">
-        <v>412</v>
+        <v>336</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B80" t="s">
-        <v>411</v>
+        <v>335</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="B81" t="s">
-        <v>410</v>
+        <v>334</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>409</v>
+        <v>333</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="B83" t="s">
-        <v>408</v>
+        <v>332</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="B84" t="s">
-        <v>407</v>
+        <v>331</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="B85" t="s">
-        <v>406</v>
+        <v>330</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>232</v>
+        <v>154</v>
       </c>
       <c r="B86" t="s">
-        <v>405</v>
+        <v>329</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="B87" t="s">
-        <v>404</v>
+        <v>328</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>251</v>
+        <v>136</v>
       </c>
       <c r="B88" t="s">
-        <v>403</v>
+        <v>327</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>263</v>
+        <v>74</v>
       </c>
       <c r="B89" t="s">
-        <v>402</v>
+        <v>326</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>223</v>
+        <v>182</v>
       </c>
       <c r="B90" t="s">
-        <v>401</v>
+        <v>325</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B91" t="s">
-        <v>400</v>
+        <v>324</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="B92" t="s">
-        <v>399</v>
+        <v>323</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>265</v>
+        <v>72</v>
       </c>
       <c r="B93" t="s">
-        <v>398</v>
+        <v>322</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="B94" t="s">
-        <v>397</v>
+        <v>321</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>212</v>
+        <v>128</v>
       </c>
       <c r="B95" t="s">
-        <v>396</v>
+        <v>320</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="B96" t="s">
-        <v>395</v>
+        <v>319</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="B97" t="s">
-        <v>394</v>
+        <v>318</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>264</v>
+        <v>130</v>
       </c>
       <c r="B98" t="s">
-        <v>393</v>
+        <v>317</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>392</v>
+        <v>316</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>204</v>
+        <v>138</v>
       </c>
       <c r="B100" t="s">
-        <v>391</v>
+        <v>315</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="B101" t="s">
-        <v>390</v>
+        <v>314</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="B102" t="s">
-        <v>389</v>
+        <v>313</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>202</v>
-      </c>
-      <c r="B103" t="s">
-        <v>388</v>
+        <v>176</v>
+      </c>
+      <c r="B103" s="1">
+        <v>98593517085.180405</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>269</v>
-      </c>
-      <c r="B104" t="s">
-        <v>387</v>
+        <v>180</v>
+      </c>
+      <c r="B104" s="1">
+        <v>97552365633.393799</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>144</v>
-      </c>
-      <c r="B105" t="s">
-        <v>386</v>
+        <v>200</v>
+      </c>
+      <c r="B105" s="1">
+        <v>93337845790.051697</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>215</v>
-      </c>
-      <c r="B106" t="s">
-        <v>385</v>
+        <v>150</v>
+      </c>
+      <c r="B106" s="1">
+        <v>85859965603.139404</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>134</v>
-      </c>
-      <c r="B107" t="s">
-        <v>384</v>
+        <v>152</v>
+      </c>
+      <c r="B107" s="1">
+        <v>78096772186.189697</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>247</v>
-      </c>
-      <c r="B108" t="s">
-        <v>383</v>
+        <v>114</v>
+      </c>
+      <c r="B108" s="1">
+        <v>73271221672.281906</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>164</v>
-      </c>
-      <c r="B109" t="s">
-        <v>382</v>
+        <v>124</v>
+      </c>
+      <c r="B109" s="1">
+        <v>66805339786.626999</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>186</v>
-      </c>
-      <c r="B110" t="s">
-        <v>381</v>
+        <v>188</v>
+      </c>
+      <c r="B110" s="1">
+        <v>507399118474.95001</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>211</v>
-      </c>
-      <c r="B111" t="s">
-        <v>380</v>
+        <v>201</v>
+      </c>
+      <c r="B111" s="1">
+        <v>470988857388.01501</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>203</v>
-      </c>
-      <c r="B112" t="s">
-        <v>379</v>
+        <v>140</v>
+      </c>
+      <c r="B112" s="1">
+        <v>4268785786.9935198</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>205</v>
-      </c>
-      <c r="B113" t="s">
-        <v>378</v>
+        <v>168</v>
+      </c>
+      <c r="B113" s="1">
+        <v>2968483048.3181801</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>188</v>
-      </c>
-      <c r="B114" t="s">
-        <v>377</v>
+        <v>146</v>
+      </c>
+      <c r="B114" s="1">
+        <v>24336213176.5453</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>225</v>
-      </c>
-      <c r="B115" t="s">
-        <v>376</v>
+        <v>175</v>
+      </c>
+      <c r="B115" s="1">
+        <v>232129557042.46201</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>240</v>
-      </c>
-      <c r="B116" t="s">
-        <v>375</v>
+        <v>178</v>
+      </c>
+      <c r="B116" s="1">
+        <v>128376763738.716</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>219</v>
-      </c>
-      <c r="B117" t="s">
-        <v>374</v>
+        <v>210</v>
+      </c>
+      <c r="B117" s="1">
+        <v>116820266902</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>174</v>
-      </c>
-      <c r="B118" t="s">
-        <v>373</v>
+        <v>192</v>
+      </c>
+      <c r="B118" s="1">
+        <v>102376272584.57401</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>195</v>
-      </c>
-      <c r="B119" t="s">
-        <v>372</v>
+        <v>211</v>
+      </c>
+      <c r="B119" s="1">
+        <v>9104747442.2610397</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>190</v>
-      </c>
-      <c r="B120" t="s">
-        <v>371</v>
+        <v>198</v>
+      </c>
+      <c r="B120" s="1">
+        <v>4177809530.5685201</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>214</v>
-      </c>
-      <c r="B121" t="s">
-        <v>370</v>
+        <v>217</v>
+      </c>
+      <c r="B121" s="1">
+        <v>2579339586.6051602</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B122" s="1">
-        <v>98611495204.838593</v>
+        <v>1590577348.50806</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="B123" s="1">
-        <v>97727623619.991699</v>
+        <v>14107923755.0397</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>64</v>
+        <v>209</v>
       </c>
       <c r="B124" s="1">
-        <v>91101637834.870193</v>
+        <v>13458235809.255699</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="B125" s="1">
-        <v>90129594338.297806</v>
+        <v>10212862782.423</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="B126" s="1">
-        <v>84972316848.523499</v>
+        <v>4491273502.6910896</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="B127" s="1">
-        <v>83240518293.057602</v>
+        <v>1666784837.08564</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="B128" s="1">
-        <v>77653400675.031097</v>
+        <v>83772676.265504897</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>268</v>
+        <v>204</v>
       </c>
       <c r="B129" s="1">
-        <v>77312107545.470596</v>
+        <v>210768792.60407501</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B130" s="1">
-        <v>66045947517.441803</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>210</v>
-      </c>
-      <c r="B131" s="1">
-        <v>60967593783.902802</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>184</v>
-      </c>
-      <c r="B132" s="1">
-        <v>57390150714.023499</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>209</v>
-      </c>
-      <c r="B133" s="1">
-        <v>57324540791.513901</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>213</v>
-      </c>
-      <c r="B134" s="1">
-        <v>57103897591.443703</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>198</v>
-      </c>
-      <c r="B135" s="1">
-        <v>52948090337.845497</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>228</v>
-      </c>
-      <c r="B136" s="1">
-        <v>47414851158.108803</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>216</v>
-      </c>
-      <c r="B137" s="1">
-        <v>447701582861.354</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>194</v>
-      </c>
-      <c r="B138" s="1">
-        <v>41325700165.145103</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>189</v>
-      </c>
-      <c r="B139" s="1">
-        <v>3876698170.2238302</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>178</v>
-      </c>
-      <c r="B140" s="1">
-        <v>38030727318.4132</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>233</v>
-      </c>
-      <c r="B141" s="1">
-        <v>367433427991.87</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>200</v>
-      </c>
-      <c r="B142" s="1">
-        <v>36031534247.663902</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>191</v>
-      </c>
-      <c r="B143" s="1">
-        <v>35587683044.202599</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>148</v>
-      </c>
-      <c r="B144" s="1">
-        <v>350247209911.375</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>231</v>
-      </c>
-      <c r="B145" s="1">
-        <v>27704489491.519299</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>206</v>
-      </c>
-      <c r="B146" s="1">
-        <v>197702428813.92099</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>176</v>
-      </c>
-      <c r="B147" s="1">
-        <v>115193279560.39301</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>162</v>
-      </c>
-      <c r="B148" s="1">
-        <v>10399536143.7679</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>222</v>
-      </c>
-      <c r="B149" s="1">
-        <v>100978179082.838</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>199</v>
-      </c>
-      <c r="B150" s="1">
-        <v>9424837849.6558208</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>239</v>
-      </c>
-      <c r="B151" s="1">
-        <v>8885621767.5071201</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>237</v>
-      </c>
-      <c r="B152" s="1">
-        <v>8075051356.5641899</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>246</v>
-      </c>
-      <c r="B153" s="1">
-        <v>7255016084.3219805</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>224</v>
-      </c>
-      <c r="B154" s="1">
-        <v>5593245600.2966995</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>230</v>
-      </c>
-      <c r="B155" s="1">
-        <v>5404868888.6323605</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>245</v>
-      </c>
-      <c r="B156" s="1">
-        <v>5147757919.2167397</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>227</v>
-      </c>
-      <c r="B157" s="1">
-        <v>4568803694.6789398</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>248</v>
-      </c>
-      <c r="B158" s="1">
-        <v>36582133343.666702</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>252</v>
-      </c>
-      <c r="B159" s="1">
-        <v>18681445001.367901</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>266</v>
-      </c>
-      <c r="B160" s="1">
-        <v>15301699204.248699</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>217</v>
-      </c>
-      <c r="B161" s="1">
-        <v>11952405479.630699</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>244</v>
-      </c>
-      <c r="B162" s="1">
-        <v>74743765.9206312</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>243</v>
-      </c>
-      <c r="B163" s="1">
-        <v>444520160.42858797</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>249</v>
-      </c>
-      <c r="B164" s="1">
-        <v>2744044710.9393802</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>241</v>
-      </c>
-      <c r="B165" s="1">
-        <v>2400463169.1354799</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>261</v>
-      </c>
-      <c r="B166" s="1">
-        <v>2300484288.0949202</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>259</v>
-      </c>
-      <c r="B167" s="1">
-        <v>1833593577.3870599</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>254</v>
-      </c>
-      <c r="B168" s="1">
-        <v>1816567397.8087599</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>262</v>
-      </c>
-      <c r="B169" s="1">
-        <v>1206468849.7021401</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>255</v>
-      </c>
-      <c r="B170" s="1">
-        <v>98685601.585811406</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>267</v>
-      </c>
-      <c r="B171" s="1">
-        <v>89842871.546010897</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>250</v>
-      </c>
-      <c r="B172" s="1">
-        <v>270016724.27211201</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>260</v>
-      </c>
-      <c r="B173" s="1">
-        <v>249872118.389388</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>253</v>
-      </c>
-      <c r="B174" s="1">
-        <v>31284460.373627901</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>242</v>
-      </c>
-      <c r="B175" s="1">
-        <v>146773.472504815</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>258</v>
-      </c>
-      <c r="B176" t="s">
-        <v>257</v>
+        <v>3909748.8562598</v>
       </c>
     </row>
   </sheetData>
@@ -6866,8 +5528,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36A91F71-3B0B-464E-B8E2-AF72B891BD4A}">
-  <dimension ref="A1:B176"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15BAE4D6-0632-45FC-8A2A-F10ADBD87A05}">
+  <dimension ref="A1:B130"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="72.85546875" bestFit="1" customWidth="1"/>
@@ -6884,106 +5546,106 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>571</v>
+        <v>493</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>570</v>
+        <v>492</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>569</v>
+        <v>491</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>568</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>567</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>566</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>565</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>564</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>563</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>562</v>
+        <v>484</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>561</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>560</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>559</v>
+        <v>481</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -6991,7 +5653,7 @@
         <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>558</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -6999,383 +5661,383 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>557</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>553</v>
+        <v>475</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>552</v>
+        <v>474</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>551</v>
+        <v>473</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>550</v>
+        <v>472</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>549</v>
+        <v>471</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>548</v>
+        <v>470</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>547</v>
+        <v>469</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>546</v>
+        <v>468</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>545</v>
+        <v>467</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>544</v>
+        <v>466</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>543</v>
+        <v>465</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>542</v>
+        <v>464</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B32" t="s">
-        <v>541</v>
+        <v>463</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>540</v>
+        <v>462</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B34" t="s">
-        <v>539</v>
+        <v>461</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B35" t="s">
-        <v>538</v>
+        <v>460</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B36" t="s">
-        <v>537</v>
+        <v>459</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>536</v>
+        <v>458</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
-        <v>535</v>
+        <v>457</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>534</v>
+        <v>456</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="B40" t="s">
-        <v>533</v>
+        <v>455</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>532</v>
+        <v>454</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B42" t="s">
-        <v>531</v>
+        <v>453</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B43" t="s">
-        <v>530</v>
+        <v>452</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B44" t="s">
-        <v>529</v>
+        <v>451</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="B45" t="s">
-        <v>528</v>
+        <v>450</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="B46" t="s">
-        <v>527</v>
+        <v>449</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B47" t="s">
-        <v>526</v>
+        <v>448</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B48" t="s">
-        <v>525</v>
+        <v>447</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="B49" t="s">
-        <v>524</v>
+        <v>446</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B50" t="s">
-        <v>523</v>
+        <v>445</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="B51" t="s">
-        <v>522</v>
+        <v>444</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B52" t="s">
-        <v>521</v>
+        <v>443</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="B53" t="s">
-        <v>520</v>
+        <v>442</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="B54" t="s">
-        <v>519</v>
+        <v>441</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B55" t="s">
-        <v>518</v>
+        <v>440</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B56" t="s">
-        <v>517</v>
+        <v>439</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="B57" t="s">
-        <v>516</v>
+        <v>438</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="B58" t="s">
-        <v>515</v>
+        <v>437</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="B59" t="s">
-        <v>514</v>
+        <v>436</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B60" t="s">
-        <v>513</v>
+        <v>435</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B61" t="s">
-        <v>512</v>
+        <v>434</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="B62" t="s">
-        <v>511</v>
+        <v>433</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="B63" t="s">
-        <v>510</v>
+        <v>432</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7383,903 +6045,535 @@
         <v>132</v>
       </c>
       <c r="B64" t="s">
-        <v>509</v>
+        <v>431</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B65" t="s">
-        <v>508</v>
+        <v>430</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>507</v>
+        <v>429</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>182</v>
+        <v>124</v>
       </c>
       <c r="B67" t="s">
-        <v>506</v>
+        <v>428</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B68" t="s">
-        <v>505</v>
+        <v>427</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="B69" t="s">
-        <v>504</v>
+        <v>426</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="B70" t="s">
-        <v>503</v>
+        <v>425</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B71" t="s">
-        <v>502</v>
+        <v>424</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>180</v>
+        <v>118</v>
       </c>
       <c r="B72" t="s">
-        <v>501</v>
+        <v>423</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="B73" t="s">
-        <v>500</v>
+        <v>422</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="B74" t="s">
-        <v>499</v>
+        <v>421</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B75" t="s">
-        <v>498</v>
+        <v>420</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B76" t="s">
-        <v>497</v>
+        <v>419</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B77" t="s">
-        <v>496</v>
+        <v>418</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="B78" t="s">
-        <v>495</v>
+        <v>417</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="B79" t="s">
-        <v>494</v>
+        <v>416</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B80" t="s">
-        <v>493</v>
+        <v>415</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B81" t="s">
-        <v>492</v>
+        <v>414</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>225</v>
-      </c>
-      <c r="B82" t="s">
-        <v>491</v>
+        <v>158</v>
+      </c>
+      <c r="B82" s="1">
+        <v>99978097023.354202</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>110</v>
-      </c>
-      <c r="B83" t="s">
-        <v>490</v>
+        <v>180</v>
+      </c>
+      <c r="B83" s="1">
+        <v>99859537545.588806</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B84" s="1">
-        <v>98687772867.999298</v>
+        <v>93547662565.467606</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="B85" s="1">
-        <v>89614494201.919006</v>
+        <v>78448627584.781601</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B86" s="1">
-        <v>8889674966.6148205</v>
+        <v>78006251321.657196</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="B87" s="1">
-        <v>88020244198.838806</v>
+        <v>76727934374.501602</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="B88" s="1">
-        <v>83847664207.685898</v>
+        <v>71964656460.1763</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B89" s="1">
-        <v>82520054620.159698</v>
+        <v>68508825817.9478</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B90" s="1">
-        <v>80999618839.814194</v>
+        <v>64943189099.224602</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B91" s="1">
-        <v>77717273453.876495</v>
+        <v>64326342358.042503</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B92" s="1">
-        <v>76823701015.076508</v>
+        <v>6367326476.4391098</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B93" s="1">
-        <v>68992528755.767807</v>
+        <v>51089945429.959099</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="B94" s="1">
-        <v>62969862358.797798</v>
+        <v>46848310449.193199</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>195</v>
+        <v>126</v>
       </c>
       <c r="B95" s="1">
-        <v>52228420596.356201</v>
+        <v>41168989606.477898</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B96" s="1">
-        <v>50552390638.3125</v>
+        <v>3616158215.3913898</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="B97" s="1">
-        <v>50170959313.041496</v>
+        <v>35580345910.171898</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="B98" s="1">
-        <v>49597238097.758003</v>
+        <v>33976949149.7314</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B99" s="1">
-        <v>431844000278.82898</v>
+        <v>293945758379.22302</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="B100" s="1">
-        <v>37935292224.217598</v>
+        <v>253256146451.832</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="B101" s="1">
-        <v>379017347733.41699</v>
+        <v>251016523928.52499</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B102" s="1">
-        <v>35846471966.625504</v>
+        <v>207368218751.797</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B103" s="1">
-        <v>340441896.79324001</v>
+        <v>184064761735.436</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B104" s="1">
-        <v>321216471534.94397</v>
+        <v>18148651555.2006</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="B105" s="1">
-        <v>29421401075.556499</v>
+        <v>17563200955.399399</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="B106" s="1">
-        <v>29217144778.716599</v>
+        <v>11440778789.3638</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B107" s="1">
-        <v>258432186140.17001</v>
+        <v>106665909140.763</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B108" s="1">
-        <v>24084193049.892502</v>
+        <v>101694242431.59599</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="B109" s="1">
-        <v>238169512285.67499</v>
+        <v>6531053237.8437996</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="B110" s="1">
-        <v>22608656586.232899</v>
+        <v>6148343002.3179598</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="B111" s="1">
-        <v>225124458616.55899</v>
+        <v>514143563.83132398</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="B112" s="1">
-        <v>209889868837.694</v>
+        <v>4111743406.6495299</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B113" s="1">
-        <v>206117780662.242</v>
+        <v>34961756536.564697</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="B114" s="1">
-        <v>19988524471.3596</v>
+        <v>30431780843.272999</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="B115" s="1">
-        <v>184831055585.02899</v>
+        <v>2668783799.7192202</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="B116" s="1">
-        <v>18145907757.428501</v>
+        <v>19315169721.063301</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B117" s="1">
-        <v>17574158609.4058</v>
+        <v>18981327418.7621</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B118" s="1">
-        <v>16762089957.3771</v>
+        <v>1732326796.3095</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="B119" s="1">
-        <v>167599265401.20599</v>
+        <v>15090163324.4025</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>208</v>
+        <v>166</v>
       </c>
       <c r="B120" s="1">
-        <v>157918290729.15799</v>
+        <v>15061687799.0137</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="B121" s="1">
-        <v>151913299387.005</v>
+        <v>14442291062.3004</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B122" s="1">
-        <v>138335509337.271</v>
+        <v>11534482173.9979</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="B123" s="1">
-        <v>123574089825.86301</v>
+        <v>930217286.59701705</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="B124" s="1">
-        <v>105526419306.35001</v>
+        <v>852611890.37739503</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B125" s="1">
-        <v>10156698876.242001</v>
+        <v>691190314.97606003</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B126" s="1">
-        <v>9988412098.2167091</v>
+        <v>474716122.906299</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="B127" s="1">
-        <v>974298276.51234198</v>
+        <v>351348797.78606999</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>229</v>
-      </c>
-      <c r="B128" s="1">
-        <v>9651018266.4900494</v>
+        <v>214</v>
+      </c>
+      <c r="B128" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>230</v>
-      </c>
-      <c r="B129" s="1">
-        <v>9260864404.9257908</v>
+        <v>208</v>
+      </c>
+      <c r="B129" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>269</v>
-      </c>
-      <c r="B130" s="1">
-        <v>909142368.63499701</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>148</v>
-      </c>
-      <c r="B131" s="1">
-        <v>8459411148.7442799</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>268</v>
-      </c>
-      <c r="B132" s="1">
-        <v>7921131104.9913902</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>227</v>
-      </c>
-      <c r="B133" s="1">
-        <v>7313841855.5960503</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>218</v>
-      </c>
-      <c r="B134" s="1">
-        <v>7157779486.1247902</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>142</v>
-      </c>
-      <c r="B135" s="1">
-        <v>6820376065.5366602</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>241</v>
-      </c>
-      <c r="B136" s="1">
-        <v>6475656540.0813303</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+        <v>216</v>
+      </c>
+      <c r="B130" t="s">
         <v>215</v>
-      </c>
-      <c r="B137" s="1">
-        <v>6385786542.15518</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>221</v>
-      </c>
-      <c r="B138" s="1">
-        <v>6121995203.9026804</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>198</v>
-      </c>
-      <c r="B139" s="1">
-        <v>5336783641.0370398</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>224</v>
-      </c>
-      <c r="B140" s="1">
-        <v>4687116473.4149704</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>249</v>
-      </c>
-      <c r="B141" s="1">
-        <v>3829827162.9777298</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>164</v>
-      </c>
-      <c r="B142" s="1">
-        <v>38078414219.593498</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>233</v>
-      </c>
-      <c r="B143" s="1">
-        <v>36947569621.501602</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>236</v>
-      </c>
-      <c r="B144" s="1">
-        <v>34828879655.741096</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>237</v>
-      </c>
-      <c r="B145" s="1">
-        <v>30884534664.331402</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>261</v>
-      </c>
-      <c r="B146" s="1">
-        <v>16499931052.941299</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>244</v>
-      </c>
-      <c r="B147" s="1">
-        <v>12788451900.9387</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>246</v>
-      </c>
-      <c r="B148" s="1">
-        <v>10396863534.0819</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>210</v>
-      </c>
-      <c r="B149" s="1">
-        <v>949300549.06295097</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>267</v>
-      </c>
-      <c r="B150" s="1">
-        <v>929955278.10564494</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>243</v>
-      </c>
-      <c r="B151" s="1">
-        <v>823899472.88247299</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>259</v>
-      </c>
-      <c r="B152" s="1">
-        <v>72907069.5459508</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>263</v>
-      </c>
-      <c r="B153" s="1">
-        <v>634921578.18764305</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>260</v>
-      </c>
-      <c r="B154" s="1">
-        <v>535068476.13999498</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>258</v>
-      </c>
-      <c r="B155" s="1">
-        <v>52990410.743060701</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>238</v>
-      </c>
-      <c r="B156" s="1">
-        <v>463545311.465657</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>239</v>
-      </c>
-      <c r="B157" s="1">
-        <v>443223843.83917803</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>216</v>
-      </c>
-      <c r="B158" s="1">
-        <v>370468932.87822199</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>247</v>
-      </c>
-      <c r="B159" s="1">
-        <v>310182986.923388</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>248</v>
-      </c>
-      <c r="B160" s="1">
-        <v>251292678.757312</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>240</v>
-      </c>
-      <c r="B161" s="1">
-        <v>226041752.73969099</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>251</v>
-      </c>
-      <c r="B162" s="1">
-        <v>2078407944.2355001</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>250</v>
-      </c>
-      <c r="B163" s="1">
-        <v>205494812.12971401</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>262</v>
-      </c>
-      <c r="B164" s="1">
-        <v>1110003282.62234</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>253</v>
-      </c>
-      <c r="B165" s="1">
-        <v>66545216.515548803</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>228</v>
-      </c>
-      <c r="B166" s="1">
-        <v>6582496.91574609</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>242</v>
-      </c>
-      <c r="B167" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>245</v>
-      </c>
-      <c r="B168" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>252</v>
-      </c>
-      <c r="B169" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>256</v>
-      </c>
-      <c r="B170" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>266</v>
-      </c>
-      <c r="B171" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>264</v>
-      </c>
-      <c r="B172" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>254</v>
-      </c>
-      <c r="B173" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>255</v>
-      </c>
-      <c r="B174" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>234</v>
-      </c>
-      <c r="B175" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>265</v>
-      </c>
-      <c r="B176" t="s">
-        <v>257</v>
       </c>
     </row>
   </sheetData>
